--- a/business_plans.xlsx
+++ b/business_plans.xlsx
@@ -8,9 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ami — Projection" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ami — Book Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ami — SaaS Market" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ecommerce homework" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Funnel" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ami — Book Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ami — SaaS Market" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ecommerce homework" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -24,7 +25,7 @@
     <numFmt numFmtId="165" formatCode="\$#,##0;[RED]&quot;($&quot;#,##0\)"/>
     <numFmt numFmtId="166" formatCode="#,##0;[Red]-#,##0"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <name val="Arial"/>
       <charset val="1"/>
@@ -105,8 +106,15 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -151,6 +159,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -208,7 +228,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -506,6 +526,14 @@
     <xf numFmtId="166" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -759,12 +787,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK31"/>
+  <dimension ref="A1:AK44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="48" customWidth="1" style="46" min="1" max="1"/>
-    <col width="14" customWidth="1" style="46" min="2" max="2"/>
-    <col width="14" customWidth="1" style="46" min="3" max="3"/>
+    <col width="50" customWidth="1" style="46" min="1" max="1"/>
+    <col width="10" customWidth="1" style="46" min="2" max="2"/>
+    <col width="50" customWidth="1" style="46" min="3" max="3"/>
     <col width="10" customWidth="1" style="46" min="4" max="4"/>
     <col width="10" customWidth="1" style="46" min="5" max="5"/>
     <col width="10" customWidth="1" style="46" min="6" max="6"/>
@@ -802,3030 +830,3675 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="90" t="inlineStr">
+      <c r="A1" s="102" t="inlineStr">
         <is>
           <t>ASSUMPTIONS (edit yellow cells)</t>
         </is>
       </c>
-      <c r="B1" s="91" t="n"/>
-      <c r="C1" s="91" t="n"/>
-      <c r="D1" s="91" t="n"/>
-      <c r="E1" s="91" t="n"/>
-      <c r="F1" s="91" t="n"/>
-      <c r="G1" s="91" t="n"/>
-      <c r="H1" s="91" t="n"/>
-      <c r="I1" s="91" t="n"/>
-      <c r="J1" s="91" t="n"/>
-      <c r="K1" s="91" t="n"/>
-      <c r="L1" s="91" t="n"/>
-      <c r="M1" s="91" t="n"/>
-      <c r="N1" s="91" t="n"/>
-      <c r="O1" s="91" t="n"/>
-      <c r="P1" s="91" t="n"/>
-      <c r="Q1" s="91" t="n"/>
-      <c r="R1" s="91" t="n"/>
-      <c r="S1" s="91" t="n"/>
-      <c r="T1" s="91" t="n"/>
-      <c r="U1" s="91" t="n"/>
-      <c r="V1" s="91" t="n"/>
-      <c r="W1" s="91" t="n"/>
-      <c r="X1" s="91" t="n"/>
-      <c r="Y1" s="91" t="n"/>
-      <c r="Z1" s="91" t="n"/>
-      <c r="AA1" s="91" t="n"/>
-      <c r="AB1" s="91" t="n"/>
-      <c r="AC1" s="91" t="n"/>
-      <c r="AD1" s="91" t="n"/>
-      <c r="AE1" s="91" t="n"/>
-      <c r="AF1" s="91" t="n"/>
-      <c r="AG1" s="91" t="n"/>
-      <c r="AH1" s="91" t="n"/>
-      <c r="AI1" s="91" t="n"/>
-      <c r="AJ1" s="91" t="n"/>
-      <c r="AK1" s="91" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="92" t="inlineStr">
+      <c r="A2" s="45" t="inlineStr">
         <is>
           <t>Email list monthly churn</t>
         </is>
       </c>
-      <c r="B2" s="93" t="n">
+      <c r="B2" s="101" t="n">
         <v>0.01</v>
       </c>
-      <c r="C2" s="91" t="inlineStr">
+      <c r="C2" s="45" t="inlineStr">
         <is>
           <t>unsubscribes / month</t>
         </is>
       </c>
-      <c r="D2" s="91" t="n"/>
-      <c r="E2" s="91" t="n"/>
-      <c r="F2" s="91" t="n"/>
-      <c r="G2" s="91" t="n"/>
-      <c r="H2" s="91" t="n"/>
-      <c r="I2" s="91" t="n"/>
-      <c r="J2" s="91" t="n"/>
-      <c r="K2" s="91" t="n"/>
-      <c r="L2" s="91" t="n"/>
-      <c r="M2" s="91" t="n"/>
-      <c r="N2" s="91" t="n"/>
-      <c r="O2" s="91" t="n"/>
-      <c r="P2" s="91" t="n"/>
-      <c r="Q2" s="91" t="n"/>
-      <c r="R2" s="91" t="n"/>
-      <c r="S2" s="91" t="n"/>
-      <c r="T2" s="91" t="n"/>
-      <c r="U2" s="91" t="n"/>
-      <c r="V2" s="91" t="n"/>
-      <c r="W2" s="91" t="n"/>
-      <c r="X2" s="91" t="n"/>
-      <c r="Y2" s="91" t="n"/>
-      <c r="Z2" s="91" t="n"/>
-      <c r="AA2" s="91" t="n"/>
-      <c r="AB2" s="91" t="n"/>
-      <c r="AC2" s="91" t="n"/>
-      <c r="AD2" s="91" t="n"/>
-      <c r="AE2" s="91" t="n"/>
-      <c r="AF2" s="91" t="n"/>
-      <c r="AG2" s="91" t="n"/>
-      <c r="AH2" s="91" t="n"/>
-      <c r="AI2" s="91" t="n"/>
-      <c r="AJ2" s="91" t="n"/>
-      <c r="AK2" s="91" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="92" t="inlineStr">
+      <c r="A3" s="45" t="inlineStr">
         <is>
           <t>Cohort price / seat</t>
         </is>
       </c>
-      <c r="B3" s="94" t="n">
+      <c r="B3" s="101" t="n">
         <v>5000</v>
       </c>
-      <c r="C3" s="91" t="inlineStr">
+      <c r="C3" s="45" t="inlineStr">
         <is>
           <t>$ — flagship 6-week cohort</t>
         </is>
       </c>
-      <c r="D3" s="91" t="n"/>
-      <c r="E3" s="91" t="n"/>
-      <c r="F3" s="91" t="n"/>
-      <c r="G3" s="91" t="n"/>
-      <c r="H3" s="91" t="n"/>
-      <c r="I3" s="91" t="n"/>
-      <c r="J3" s="91" t="n"/>
-      <c r="K3" s="91" t="n"/>
-      <c r="L3" s="91" t="n"/>
-      <c r="M3" s="91" t="n"/>
-      <c r="N3" s="91" t="n"/>
-      <c r="O3" s="91" t="n"/>
-      <c r="P3" s="91" t="n"/>
-      <c r="Q3" s="91" t="n"/>
-      <c r="R3" s="91" t="n"/>
-      <c r="S3" s="91" t="n"/>
-      <c r="T3" s="91" t="n"/>
-      <c r="U3" s="91" t="n"/>
-      <c r="V3" s="91" t="n"/>
-      <c r="W3" s="91" t="n"/>
-      <c r="X3" s="91" t="n"/>
-      <c r="Y3" s="91" t="n"/>
-      <c r="Z3" s="91" t="n"/>
-      <c r="AA3" s="91" t="n"/>
-      <c r="AB3" s="91" t="n"/>
-      <c r="AC3" s="91" t="n"/>
-      <c r="AD3" s="91" t="n"/>
-      <c r="AE3" s="91" t="n"/>
-      <c r="AF3" s="91" t="n"/>
-      <c r="AG3" s="91" t="n"/>
-      <c r="AH3" s="91" t="n"/>
-      <c r="AI3" s="91" t="n"/>
-      <c r="AJ3" s="91" t="n"/>
-      <c r="AK3" s="91" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="92" t="inlineStr">
-        <is>
-          <t>Cohort seats / run</t>
-        </is>
-      </c>
-      <c r="B4" s="95" t="n">
+      <c r="A4" s="45" t="inlineStr">
+        <is>
+          <t>Cohort capacity (max seats / run)</t>
+        </is>
+      </c>
+      <c r="B4" s="101" t="n">
+        <v>12</v>
+      </c>
+      <c r="C4" s="45" t="inlineStr">
+        <is>
+          <t>soft cap; informational only</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="45" t="inlineStr">
+        <is>
+          <t>Paid challenge — standard ticket</t>
+        </is>
+      </c>
+      <c r="B5" s="101" t="n">
+        <v>97</v>
+      </c>
+      <c r="C5" s="45" t="inlineStr">
+        <is>
+          <t>$ — 5-day pre-cohort GA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="45" t="inlineStr">
+        <is>
+          <t>Paid challenge — VIP ticket</t>
+        </is>
+      </c>
+      <c r="B6" s="101" t="n">
+        <v>297</v>
+      </c>
+      <c r="C6" s="45" t="inlineStr">
+        <is>
+          <t>$ — 5-day VIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="45" t="inlineStr">
+        <is>
+          <t>SaaS annual fee / customer</t>
+        </is>
+      </c>
+      <c r="B7" s="101" t="n">
+        <v>25000</v>
+      </c>
+      <c r="C7" s="45" t="inlineStr">
+        <is>
+          <t>$/yr — RE wire-fraud, Phase 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="45" t="inlineStr">
+        <is>
+          <t>SaaS annual attrition</t>
+        </is>
+      </c>
+      <c r="B8" s="101" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C8" s="45" t="inlineStr">
+        <is>
+          <t>fraction not renewing</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="45" t="inlineStr">
+        <is>
+          <t>Platform / tooling overhead / mo</t>
+        </is>
+      </c>
+      <c r="B9" s="101" t="n">
+        <v>50</v>
+      </c>
+      <c r="C9" s="45" t="inlineStr">
+        <is>
+          <t>$/month — Listmonk VPS + tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="45" t="inlineStr">
+        <is>
+          <t>Server unit cost / month</t>
+        </is>
+      </c>
+      <c r="B10" s="101" t="n">
+        <v>50</v>
+      </c>
+      <c r="C10" s="45" t="inlineStr">
+        <is>
+          <t>$/month per OVH unit (incl backups)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="45" t="inlineStr">
+        <is>
+          <t>Payment plan adoption %</t>
+        </is>
+      </c>
+      <c r="B11" s="101" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="C11" s="45" t="inlineStr">
+        <is>
+          <t>fraction of cohort buyers choosing N-pay</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="45" t="inlineStr">
+        <is>
+          <t>Payment plan months</t>
+        </is>
+      </c>
+      <c r="B12" s="101" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" s="45" t="inlineStr">
+        <is>
+          <t>months across which plan is split</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="45" t="inlineStr">
+        <is>
+          <t>Payment plan price uplift %</t>
+        </is>
+      </c>
+      <c r="B13" s="101" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C13" s="45" t="inlineStr">
+        <is>
+          <t>small markup vs lump sum</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="45" t="inlineStr">
+        <is>
+          <t>Card processing fee %</t>
+        </is>
+      </c>
+      <c r="B14" s="101" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="C14" s="45" t="inlineStr">
+        <is>
+          <t>Stripe/Invoice4U typical</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="45" t="inlineStr">
+        <is>
+          <t>Card processing fee fixed $</t>
+        </is>
+      </c>
+      <c r="B15" s="101" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C15" s="45" t="inlineStr">
+        <is>
+          <t>per transaction</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="45" t="inlineStr">
+        <is>
+          <t>Cohort gross margin assumption</t>
+        </is>
+      </c>
+      <c r="B16" s="101" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="C16" s="45" t="inlineStr">
+        <is>
+          <t>after processing + plan uplift offset</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="102" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B18" s="45" t="inlineStr">
+        <is>
+          <t>Year 1 (May 2026 – Apr 2027)</t>
+        </is>
+      </c>
+      <c r="N18" s="45" t="inlineStr">
+        <is>
+          <t>Year 2 (May 2027 – Apr 2028)</t>
+        </is>
+      </c>
+      <c r="Z18" s="45" t="inlineStr">
+        <is>
+          <t>Year 3 (May 2028 – Apr 2029)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="102" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B19" s="45" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="C19" s="45" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="D19" s="45" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="E19" s="45" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="F19" s="45" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="G19" s="45" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="H19" s="45" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="I19" s="45" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="J19" s="45" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="K19" s="45" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="L19" s="45" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="M19" s="45" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="N19" s="45" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="O19" s="45" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="P19" s="45" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="Q19" s="45" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="R19" s="45" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="S19" s="45" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="T19" s="45" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="U19" s="45" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="V19" s="45" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="W19" s="45" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="X19" s="45" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="Y19" s="45" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="Z19" s="45" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="AA19" s="45" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="AB19" s="45" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="AC19" s="45" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="AD19" s="45" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="AE19" s="45" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="AF19" s="45" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="AG19" s="45" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="AH19" s="45" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="AI19" s="45" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="AJ19" s="45" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="AK19" s="45" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="45" t="inlineStr">
+        <is>
+          <t>New email subscribers / month</t>
+        </is>
+      </c>
+      <c r="B20" s="101" t="n">
+        <v>5</v>
+      </c>
+      <c r="C20" s="101" t="n">
+        <v>10</v>
+      </c>
+      <c r="D20" s="101" t="n">
+        <v>30</v>
+      </c>
+      <c r="E20" s="101" t="n">
+        <v>25</v>
+      </c>
+      <c r="F20" s="101" t="n">
+        <v>30</v>
+      </c>
+      <c r="G20" s="101" t="n">
+        <v>50</v>
+      </c>
+      <c r="H20" s="101" t="n">
+        <v>35</v>
+      </c>
+      <c r="I20" s="101" t="n">
+        <v>35</v>
+      </c>
+      <c r="J20" s="101" t="n">
+        <v>60</v>
+      </c>
+      <c r="K20" s="101" t="n">
+        <v>45</v>
+      </c>
+      <c r="L20" s="101" t="n">
+        <v>50</v>
+      </c>
+      <c r="M20" s="101" t="n">
+        <v>70</v>
+      </c>
+      <c r="N20" s="101" t="n">
+        <v>75</v>
+      </c>
+      <c r="O20" s="101" t="n">
+        <v>80</v>
+      </c>
+      <c r="P20" s="101" t="n">
+        <v>95</v>
+      </c>
+      <c r="Q20" s="101" t="n">
+        <v>85</v>
+      </c>
+      <c r="R20" s="101" t="n">
+        <v>90</v>
+      </c>
+      <c r="S20" s="101" t="n">
+        <v>105</v>
+      </c>
+      <c r="T20" s="101" t="n">
+        <v>95</v>
+      </c>
+      <c r="U20" s="101" t="n">
+        <v>95</v>
+      </c>
+      <c r="V20" s="101" t="n">
+        <v>115</v>
+      </c>
+      <c r="W20" s="101" t="n">
+        <v>105</v>
+      </c>
+      <c r="X20" s="101" t="n">
+        <v>110</v>
+      </c>
+      <c r="Y20" s="101" t="n">
+        <v>125</v>
+      </c>
+      <c r="Z20" s="101" t="n">
+        <v>130</v>
+      </c>
+      <c r="AA20" s="101" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB20" s="101" t="n">
+        <v>150</v>
+      </c>
+      <c r="AC20" s="101" t="n">
+        <v>140</v>
+      </c>
+      <c r="AD20" s="101" t="n">
+        <v>145</v>
+      </c>
+      <c r="AE20" s="101" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF20" s="101" t="n">
+        <v>150</v>
+      </c>
+      <c r="AG20" s="101" t="n">
+        <v>150</v>
+      </c>
+      <c r="AH20" s="101" t="n">
+        <v>170</v>
+      </c>
+      <c r="AI20" s="101" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ20" s="101" t="n">
+        <v>165</v>
+      </c>
+      <c r="AK20" s="101" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="45" t="inlineStr">
+        <is>
+          <t>Email list size</t>
+        </is>
+      </c>
+      <c r="B21" s="103">
+        <f>B20</f>
+        <v/>
+      </c>
+      <c r="C21" s="103">
+        <f>B21*(1-$B$2)+C20</f>
+        <v/>
+      </c>
+      <c r="D21" s="103">
+        <f>C21*(1-$B$2)+D20</f>
+        <v/>
+      </c>
+      <c r="E21" s="103">
+        <f>D21*(1-$B$2)+E20</f>
+        <v/>
+      </c>
+      <c r="F21" s="103">
+        <f>E21*(1-$B$2)+F20</f>
+        <v/>
+      </c>
+      <c r="G21" s="103">
+        <f>F21*(1-$B$2)+G20</f>
+        <v/>
+      </c>
+      <c r="H21" s="103">
+        <f>G21*(1-$B$2)+H20</f>
+        <v/>
+      </c>
+      <c r="I21" s="103">
+        <f>H21*(1-$B$2)+I20</f>
+        <v/>
+      </c>
+      <c r="J21" s="103">
+        <f>I21*(1-$B$2)+J20</f>
+        <v/>
+      </c>
+      <c r="K21" s="103">
+        <f>J21*(1-$B$2)+K20</f>
+        <v/>
+      </c>
+      <c r="L21" s="103">
+        <f>K21*(1-$B$2)+L20</f>
+        <v/>
+      </c>
+      <c r="M21" s="103">
+        <f>L21*(1-$B$2)+M20</f>
+        <v/>
+      </c>
+      <c r="N21" s="103">
+        <f>M21*(1-$B$2)+N20</f>
+        <v/>
+      </c>
+      <c r="O21" s="103">
+        <f>N21*(1-$B$2)+O20</f>
+        <v/>
+      </c>
+      <c r="P21" s="103">
+        <f>O21*(1-$B$2)+P20</f>
+        <v/>
+      </c>
+      <c r="Q21" s="103">
+        <f>P21*(1-$B$2)+Q20</f>
+        <v/>
+      </c>
+      <c r="R21" s="103">
+        <f>Q21*(1-$B$2)+R20</f>
+        <v/>
+      </c>
+      <c r="S21" s="103">
+        <f>R21*(1-$B$2)+S20</f>
+        <v/>
+      </c>
+      <c r="T21" s="103">
+        <f>S21*(1-$B$2)+T20</f>
+        <v/>
+      </c>
+      <c r="U21" s="103">
+        <f>T21*(1-$B$2)+U20</f>
+        <v/>
+      </c>
+      <c r="V21" s="103">
+        <f>U21*(1-$B$2)+V20</f>
+        <v/>
+      </c>
+      <c r="W21" s="103">
+        <f>V21*(1-$B$2)+W20</f>
+        <v/>
+      </c>
+      <c r="X21" s="103">
+        <f>W21*(1-$B$2)+X20</f>
+        <v/>
+      </c>
+      <c r="Y21" s="103">
+        <f>X21*(1-$B$2)+Y20</f>
+        <v/>
+      </c>
+      <c r="Z21" s="103">
+        <f>Y21*(1-$B$2)+Z20</f>
+        <v/>
+      </c>
+      <c r="AA21" s="103">
+        <f>Z21*(1-$B$2)+AA20</f>
+        <v/>
+      </c>
+      <c r="AB21" s="103">
+        <f>AA21*(1-$B$2)+AB20</f>
+        <v/>
+      </c>
+      <c r="AC21" s="103">
+        <f>AB21*(1-$B$2)+AC20</f>
+        <v/>
+      </c>
+      <c r="AD21" s="103">
+        <f>AC21*(1-$B$2)+AD20</f>
+        <v/>
+      </c>
+      <c r="AE21" s="103">
+        <f>AD21*(1-$B$2)+AE20</f>
+        <v/>
+      </c>
+      <c r="AF21" s="103">
+        <f>AE21*(1-$B$2)+AF20</f>
+        <v/>
+      </c>
+      <c r="AG21" s="103">
+        <f>AF21*(1-$B$2)+AG20</f>
+        <v/>
+      </c>
+      <c r="AH21" s="103">
+        <f>AG21*(1-$B$2)+AH20</f>
+        <v/>
+      </c>
+      <c r="AI21" s="103">
+        <f>AH21*(1-$B$2)+AI20</f>
+        <v/>
+      </c>
+      <c r="AJ21" s="103">
+        <f>AI21*(1-$B$2)+AJ20</f>
+        <v/>
+      </c>
+      <c r="AK21" s="103">
+        <f>AJ21*(1-$B$2)+AK20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="45" t="inlineStr">
+        <is>
+          <t>Paid challenge — standard tickets / month</t>
+        </is>
+      </c>
+      <c r="B22" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="101" t="n">
+        <v>25</v>
+      </c>
+      <c r="E22" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="101" t="n">
+        <v>30</v>
+      </c>
+      <c r="H22" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="101" t="n">
+        <v>35</v>
+      </c>
+      <c r="K22" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="101" t="n">
+        <v>40</v>
+      </c>
+      <c r="N22" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="101" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q22" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="101" t="n">
+        <v>50</v>
+      </c>
+      <c r="T22" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="101" t="n">
+        <v>55</v>
+      </c>
+      <c r="W22" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="101" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z22" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="101" t="n">
+        <v>60</v>
+      </c>
+      <c r="AC22" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="101" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF22" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="101" t="n">
+        <v>70</v>
+      </c>
+      <c r="AI22" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" s="101" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="45" t="inlineStr">
+        <is>
+          <t>Paid challenge — VIP tickets / month</t>
+        </is>
+      </c>
+      <c r="B23" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="101" t="n">
+        <v>5</v>
+      </c>
+      <c r="E23" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="101" t="n">
+        <v>6</v>
+      </c>
+      <c r="H23" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="101" t="n">
+        <v>7</v>
+      </c>
+      <c r="K23" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="101" t="n">
         <v>8</v>
       </c>
-      <c r="C4" s="91" t="inlineStr">
-        <is>
-          <t>mid of 5-10 target</t>
-        </is>
-      </c>
-      <c r="D4" s="91" t="n"/>
-      <c r="E4" s="91" t="n"/>
-      <c r="F4" s="91" t="n"/>
-      <c r="G4" s="91" t="n"/>
-      <c r="H4" s="91" t="n"/>
-      <c r="I4" s="91" t="n"/>
-      <c r="J4" s="91" t="n"/>
-      <c r="K4" s="91" t="n"/>
-      <c r="L4" s="91" t="n"/>
-      <c r="M4" s="91" t="n"/>
-      <c r="N4" s="91" t="n"/>
-      <c r="O4" s="91" t="n"/>
-      <c r="P4" s="91" t="n"/>
-      <c r="Q4" s="91" t="n"/>
-      <c r="R4" s="91" t="n"/>
-      <c r="S4" s="91" t="n"/>
-      <c r="T4" s="91" t="n"/>
-      <c r="U4" s="91" t="n"/>
-      <c r="V4" s="91" t="n"/>
-      <c r="W4" s="91" t="n"/>
-      <c r="X4" s="91" t="n"/>
-      <c r="Y4" s="91" t="n"/>
-      <c r="Z4" s="91" t="n"/>
-      <c r="AA4" s="91" t="n"/>
-      <c r="AB4" s="91" t="n"/>
-      <c r="AC4" s="91" t="n"/>
-      <c r="AD4" s="91" t="n"/>
-      <c r="AE4" s="91" t="n"/>
-      <c r="AF4" s="91" t="n"/>
-      <c r="AG4" s="91" t="n"/>
-      <c r="AH4" s="91" t="n"/>
-      <c r="AI4" s="91" t="n"/>
-      <c r="AJ4" s="91" t="n"/>
-      <c r="AK4" s="91" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="92" t="inlineStr">
-        <is>
-          <t>Paid challenge — standard ticket</t>
-        </is>
-      </c>
-      <c r="B5" s="95" t="n">
-        <v>97</v>
-      </c>
-      <c r="C5" s="91" t="inlineStr">
-        <is>
-          <t>$ — 5-day pre-cohort challenge GA</t>
-        </is>
-      </c>
-      <c r="D5" s="91" t="n"/>
-      <c r="E5" s="91" t="n"/>
-      <c r="F5" s="91" t="n"/>
-      <c r="G5" s="91" t="n"/>
-      <c r="H5" s="91" t="n"/>
-      <c r="I5" s="91" t="n"/>
-      <c r="J5" s="91" t="n"/>
-      <c r="K5" s="91" t="n"/>
-      <c r="L5" s="91" t="n"/>
-      <c r="M5" s="91" t="n"/>
-      <c r="N5" s="91" t="n"/>
-      <c r="O5" s="91" t="n"/>
-      <c r="P5" s="91" t="n"/>
-      <c r="Q5" s="91" t="n"/>
-      <c r="R5" s="91" t="n"/>
-      <c r="S5" s="91" t="n"/>
-      <c r="T5" s="91" t="n"/>
-      <c r="U5" s="91" t="n"/>
-      <c r="V5" s="91" t="n"/>
-      <c r="W5" s="91" t="n"/>
-      <c r="X5" s="91" t="n"/>
-      <c r="Y5" s="91" t="n"/>
-      <c r="Z5" s="91" t="n"/>
-      <c r="AA5" s="91" t="n"/>
-      <c r="AB5" s="91" t="n"/>
-      <c r="AC5" s="91" t="n"/>
-      <c r="AD5" s="91" t="n"/>
-      <c r="AE5" s="91" t="n"/>
-      <c r="AF5" s="91" t="n"/>
-      <c r="AG5" s="91" t="n"/>
-      <c r="AH5" s="91" t="n"/>
-      <c r="AI5" s="91" t="n"/>
-      <c r="AJ5" s="91" t="n"/>
-      <c r="AK5" s="91" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="92" t="inlineStr">
-        <is>
-          <t>Paid challenge — VIP ticket</t>
-        </is>
-      </c>
-      <c r="B6" s="95" t="n">
-        <v>297</v>
-      </c>
-      <c r="C6" s="91" t="inlineStr">
-        <is>
-          <t>$ — 5-day challenge VIP</t>
-        </is>
-      </c>
-      <c r="D6" s="91" t="n"/>
-      <c r="E6" s="91" t="n"/>
-      <c r="F6" s="91" t="n"/>
-      <c r="G6" s="91" t="n"/>
-      <c r="H6" s="91" t="n"/>
-      <c r="I6" s="91" t="n"/>
-      <c r="J6" s="91" t="n"/>
-      <c r="K6" s="91" t="n"/>
-      <c r="L6" s="91" t="n"/>
-      <c r="M6" s="91" t="n"/>
-      <c r="N6" s="91" t="n"/>
-      <c r="O6" s="91" t="n"/>
-      <c r="P6" s="91" t="n"/>
-      <c r="Q6" s="91" t="n"/>
-      <c r="R6" s="91" t="n"/>
-      <c r="S6" s="91" t="n"/>
-      <c r="T6" s="91" t="n"/>
-      <c r="U6" s="91" t="n"/>
-      <c r="V6" s="91" t="n"/>
-      <c r="W6" s="91" t="n"/>
-      <c r="X6" s="91" t="n"/>
-      <c r="Y6" s="91" t="n"/>
-      <c r="Z6" s="91" t="n"/>
-      <c r="AA6" s="91" t="n"/>
-      <c r="AB6" s="91" t="n"/>
-      <c r="AC6" s="91" t="n"/>
-      <c r="AD6" s="91" t="n"/>
-      <c r="AE6" s="91" t="n"/>
-      <c r="AF6" s="91" t="n"/>
-      <c r="AG6" s="91" t="n"/>
-      <c r="AH6" s="91" t="n"/>
-      <c r="AI6" s="91" t="n"/>
-      <c r="AJ6" s="91" t="n"/>
-      <c r="AK6" s="91" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="92" t="inlineStr">
-        <is>
-          <t>SaaS annual fee / customer</t>
-        </is>
-      </c>
-      <c r="B7" s="94" t="n">
-        <v>25000</v>
-      </c>
-      <c r="C7" s="91" t="inlineStr">
-        <is>
-          <t>$/yr — RE wire-fraud, Phase 2</t>
-        </is>
-      </c>
-      <c r="D7" s="91" t="n"/>
-      <c r="E7" s="91" t="n"/>
-      <c r="F7" s="91" t="n"/>
-      <c r="G7" s="91" t="n"/>
-      <c r="H7" s="91" t="n"/>
-      <c r="I7" s="91" t="n"/>
-      <c r="J7" s="91" t="n"/>
-      <c r="K7" s="91" t="n"/>
-      <c r="L7" s="91" t="n"/>
-      <c r="M7" s="91" t="n"/>
-      <c r="N7" s="91" t="n"/>
-      <c r="O7" s="91" t="n"/>
-      <c r="P7" s="91" t="n"/>
-      <c r="Q7" s="91" t="n"/>
-      <c r="R7" s="91" t="n"/>
-      <c r="S7" s="91" t="n"/>
-      <c r="T7" s="91" t="n"/>
-      <c r="U7" s="91" t="n"/>
-      <c r="V7" s="91" t="n"/>
-      <c r="W7" s="91" t="n"/>
-      <c r="X7" s="91" t="n"/>
-      <c r="Y7" s="91" t="n"/>
-      <c r="Z7" s="91" t="n"/>
-      <c r="AA7" s="91" t="n"/>
-      <c r="AB7" s="91" t="n"/>
-      <c r="AC7" s="91" t="n"/>
-      <c r="AD7" s="91" t="n"/>
-      <c r="AE7" s="91" t="n"/>
-      <c r="AF7" s="91" t="n"/>
-      <c r="AG7" s="91" t="n"/>
-      <c r="AH7" s="91" t="n"/>
-      <c r="AI7" s="91" t="n"/>
-      <c r="AJ7" s="91" t="n"/>
-      <c r="AK7" s="91" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="92" t="inlineStr">
-        <is>
-          <t>SaaS annual attrition</t>
-        </is>
-      </c>
-      <c r="B8" s="93" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C8" s="91" t="inlineStr">
-        <is>
-          <t>fraction not renewing</t>
-        </is>
-      </c>
-      <c r="D8" s="91" t="n"/>
-      <c r="E8" s="91" t="n"/>
-      <c r="F8" s="91" t="n"/>
-      <c r="G8" s="91" t="n"/>
-      <c r="H8" s="91" t="n"/>
-      <c r="I8" s="91" t="n"/>
-      <c r="J8" s="91" t="n"/>
-      <c r="K8" s="91" t="n"/>
-      <c r="L8" s="91" t="n"/>
-      <c r="M8" s="91" t="n"/>
-      <c r="N8" s="91" t="n"/>
-      <c r="O8" s="91" t="n"/>
-      <c r="P8" s="91" t="n"/>
-      <c r="Q8" s="91" t="n"/>
-      <c r="R8" s="91" t="n"/>
-      <c r="S8" s="91" t="n"/>
-      <c r="T8" s="91" t="n"/>
-      <c r="U8" s="91" t="n"/>
-      <c r="V8" s="91" t="n"/>
-      <c r="W8" s="91" t="n"/>
-      <c r="X8" s="91" t="n"/>
-      <c r="Y8" s="91" t="n"/>
-      <c r="Z8" s="91" t="n"/>
-      <c r="AA8" s="91" t="n"/>
-      <c r="AB8" s="91" t="n"/>
-      <c r="AC8" s="91" t="n"/>
-      <c r="AD8" s="91" t="n"/>
-      <c r="AE8" s="91" t="n"/>
-      <c r="AF8" s="91" t="n"/>
-      <c r="AG8" s="91" t="n"/>
-      <c r="AH8" s="91" t="n"/>
-      <c r="AI8" s="91" t="n"/>
-      <c r="AJ8" s="91" t="n"/>
-      <c r="AK8" s="91" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="92" t="inlineStr">
-        <is>
-          <t>Platform / tooling overhead / month</t>
-        </is>
-      </c>
-      <c r="B9" s="95" t="n">
-        <v>50</v>
-      </c>
-      <c r="C9" s="91" t="inlineStr">
-        <is>
-          <t>$/month — Listmonk VPS + tools</t>
-        </is>
-      </c>
-      <c r="D9" s="91" t="n"/>
-      <c r="E9" s="91" t="n"/>
-      <c r="F9" s="91" t="n"/>
-      <c r="G9" s="91" t="n"/>
-      <c r="H9" s="91" t="n"/>
-      <c r="I9" s="91" t="n"/>
-      <c r="J9" s="91" t="n"/>
-      <c r="K9" s="91" t="n"/>
-      <c r="L9" s="91" t="n"/>
-      <c r="M9" s="91" t="n"/>
-      <c r="N9" s="91" t="n"/>
-      <c r="O9" s="91" t="n"/>
-      <c r="P9" s="91" t="n"/>
-      <c r="Q9" s="91" t="n"/>
-      <c r="R9" s="91" t="n"/>
-      <c r="S9" s="91" t="n"/>
-      <c r="T9" s="91" t="n"/>
-      <c r="U9" s="91" t="n"/>
-      <c r="V9" s="91" t="n"/>
-      <c r="W9" s="91" t="n"/>
-      <c r="X9" s="91" t="n"/>
-      <c r="Y9" s="91" t="n"/>
-      <c r="Z9" s="91" t="n"/>
-      <c r="AA9" s="91" t="n"/>
-      <c r="AB9" s="91" t="n"/>
-      <c r="AC9" s="91" t="n"/>
-      <c r="AD9" s="91" t="n"/>
-      <c r="AE9" s="91" t="n"/>
-      <c r="AF9" s="91" t="n"/>
-      <c r="AG9" s="91" t="n"/>
-      <c r="AH9" s="91" t="n"/>
-      <c r="AI9" s="91" t="n"/>
-      <c r="AJ9" s="91" t="n"/>
-      <c r="AK9" s="91" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="92" t="inlineStr">
-        <is>
-          <t>Server unit cost / month</t>
-        </is>
-      </c>
-      <c r="B10" s="95" t="n">
-        <v>50</v>
-      </c>
-      <c r="C10" s="91" t="inlineStr">
-        <is>
-          <t>$/month per OVH unit (incl. backups)</t>
-        </is>
-      </c>
-      <c r="D10" s="91" t="n"/>
-      <c r="E10" s="91" t="n"/>
-      <c r="F10" s="91" t="n"/>
-      <c r="G10" s="91" t="n"/>
-      <c r="H10" s="91" t="n"/>
-      <c r="I10" s="91" t="n"/>
-      <c r="J10" s="91" t="n"/>
-      <c r="K10" s="91" t="n"/>
-      <c r="L10" s="91" t="n"/>
-      <c r="M10" s="91" t="n"/>
-      <c r="N10" s="91" t="n"/>
-      <c r="O10" s="91" t="n"/>
-      <c r="P10" s="91" t="n"/>
-      <c r="Q10" s="91" t="n"/>
-      <c r="R10" s="91" t="n"/>
-      <c r="S10" s="91" t="n"/>
-      <c r="T10" s="91" t="n"/>
-      <c r="U10" s="91" t="n"/>
-      <c r="V10" s="91" t="n"/>
-      <c r="W10" s="91" t="n"/>
-      <c r="X10" s="91" t="n"/>
-      <c r="Y10" s="91" t="n"/>
-      <c r="Z10" s="91" t="n"/>
-      <c r="AA10" s="91" t="n"/>
-      <c r="AB10" s="91" t="n"/>
-      <c r="AC10" s="91" t="n"/>
-      <c r="AD10" s="91" t="n"/>
-      <c r="AE10" s="91" t="n"/>
-      <c r="AF10" s="91" t="n"/>
-      <c r="AG10" s="91" t="n"/>
-      <c r="AH10" s="91" t="n"/>
-      <c r="AI10" s="91" t="n"/>
-      <c r="AJ10" s="91" t="n"/>
-      <c r="AK10" s="91" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="96" t="n"/>
-      <c r="B11" s="91" t="n"/>
-      <c r="C11" s="91" t="n"/>
-      <c r="D11" s="91" t="n"/>
-      <c r="E11" s="91" t="n"/>
-      <c r="F11" s="91" t="n"/>
-      <c r="G11" s="91" t="n"/>
-      <c r="H11" s="91" t="n"/>
-      <c r="I11" s="91" t="n"/>
-      <c r="J11" s="91" t="n"/>
-      <c r="K11" s="91" t="n"/>
-      <c r="L11" s="91" t="n"/>
-      <c r="M11" s="91" t="n"/>
-      <c r="N11" s="91" t="n"/>
-      <c r="O11" s="91" t="n"/>
-      <c r="P11" s="91" t="n"/>
-      <c r="Q11" s="91" t="n"/>
-      <c r="R11" s="91" t="n"/>
-      <c r="S11" s="91" t="n"/>
-      <c r="T11" s="91" t="n"/>
-      <c r="U11" s="91" t="n"/>
-      <c r="V11" s="91" t="n"/>
-      <c r="W11" s="91" t="n"/>
-      <c r="X11" s="91" t="n"/>
-      <c r="Y11" s="91" t="n"/>
-      <c r="Z11" s="91" t="n"/>
-      <c r="AA11" s="91" t="n"/>
-      <c r="AB11" s="91" t="n"/>
-      <c r="AC11" s="91" t="n"/>
-      <c r="AD11" s="91" t="n"/>
-      <c r="AE11" s="91" t="n"/>
-      <c r="AF11" s="91" t="n"/>
-      <c r="AG11" s="91" t="n"/>
-      <c r="AH11" s="91" t="n"/>
-      <c r="AI11" s="91" t="n"/>
-      <c r="AJ11" s="91" t="n"/>
-      <c r="AK11" s="91" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="92" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B12" s="98" t="inlineStr">
-        <is>
-          <t>Year 1 (May 2026 – Apr 2027)</t>
-        </is>
-      </c>
-      <c r="N12" s="98" t="inlineStr">
-        <is>
-          <t>Year 2 (May 2027 – Apr 2028)</t>
-        </is>
-      </c>
-      <c r="Z12" s="98" t="inlineStr">
-        <is>
-          <t>Year 3 (May 2028 – Apr 2029)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="92" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B13" s="98" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="C13" s="98" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="D13" s="98" t="inlineStr">
-        <is>
-          <t>Jul</t>
-        </is>
-      </c>
-      <c r="E13" s="98" t="inlineStr">
-        <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="F13" s="98" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="G13" s="98" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="H13" s="98" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="I13" s="98" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="J13" s="98" t="inlineStr">
-        <is>
-          <t>Jan</t>
-        </is>
-      </c>
-      <c r="K13" s="98" t="inlineStr">
-        <is>
-          <t>Feb</t>
-        </is>
-      </c>
-      <c r="L13" s="98" t="inlineStr">
-        <is>
-          <t>Mar</t>
-        </is>
-      </c>
-      <c r="M13" s="98" t="inlineStr">
-        <is>
-          <t>Apr</t>
-        </is>
-      </c>
-      <c r="N13" s="98" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="O13" s="98" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="P13" s="98" t="inlineStr">
-        <is>
-          <t>Jul</t>
-        </is>
-      </c>
-      <c r="Q13" s="98" t="inlineStr">
-        <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="R13" s="98" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="S13" s="98" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="T13" s="98" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="U13" s="98" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="V13" s="98" t="inlineStr">
-        <is>
-          <t>Jan</t>
-        </is>
-      </c>
-      <c r="W13" s="98" t="inlineStr">
-        <is>
-          <t>Feb</t>
-        </is>
-      </c>
-      <c r="X13" s="98" t="inlineStr">
-        <is>
-          <t>Mar</t>
-        </is>
-      </c>
-      <c r="Y13" s="98" t="inlineStr">
-        <is>
-          <t>Apr</t>
-        </is>
-      </c>
-      <c r="Z13" s="98" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="AA13" s="98" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="AB13" s="98" t="inlineStr">
-        <is>
-          <t>Jul</t>
-        </is>
-      </c>
-      <c r="AC13" s="98" t="inlineStr">
-        <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="AD13" s="98" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="AE13" s="98" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="AF13" s="98" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="AG13" s="98" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="AH13" s="98" t="inlineStr">
-        <is>
-          <t>Jan</t>
-        </is>
-      </c>
-      <c r="AI13" s="98" t="inlineStr">
-        <is>
-          <t>Feb</t>
-        </is>
-      </c>
-      <c r="AJ13" s="98" t="inlineStr">
-        <is>
-          <t>Mar</t>
-        </is>
-      </c>
-      <c r="AK13" s="98" t="inlineStr">
-        <is>
-          <t>Apr</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="92" t="inlineStr">
-        <is>
-          <t>New email subscribers / month</t>
-        </is>
-      </c>
-      <c r="B14" s="95" t="n">
+      <c r="N23" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="101" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q23" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" s="101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="101" t="n">
+        <v>11</v>
+      </c>
+      <c r="W23" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="101" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z23" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="101" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC23" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="101" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF23" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" s="101" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI23" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" s="101" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="45" t="inlineStr">
+        <is>
+          <t>Challenge revenue</t>
+        </is>
+      </c>
+      <c r="B24" s="103">
+        <f>B22*$B$5+B23*$B$6</f>
+        <v/>
+      </c>
+      <c r="C24" s="103">
+        <f>C22*$B$5+C23*$B$6</f>
+        <v/>
+      </c>
+      <c r="D24" s="103">
+        <f>D22*$B$5+D23*$B$6</f>
+        <v/>
+      </c>
+      <c r="E24" s="103">
+        <f>E22*$B$5+E23*$B$6</f>
+        <v/>
+      </c>
+      <c r="F24" s="103">
+        <f>F22*$B$5+F23*$B$6</f>
+        <v/>
+      </c>
+      <c r="G24" s="103">
+        <f>G22*$B$5+G23*$B$6</f>
+        <v/>
+      </c>
+      <c r="H24" s="103">
+        <f>H22*$B$5+H23*$B$6</f>
+        <v/>
+      </c>
+      <c r="I24" s="103">
+        <f>I22*$B$5+I23*$B$6</f>
+        <v/>
+      </c>
+      <c r="J24" s="103">
+        <f>J22*$B$5+J23*$B$6</f>
+        <v/>
+      </c>
+      <c r="K24" s="103">
+        <f>K22*$B$5+K23*$B$6</f>
+        <v/>
+      </c>
+      <c r="L24" s="103">
+        <f>L22*$B$5+L23*$B$6</f>
+        <v/>
+      </c>
+      <c r="M24" s="103">
+        <f>M22*$B$5+M23*$B$6</f>
+        <v/>
+      </c>
+      <c r="N24" s="103">
+        <f>N22*$B$5+N23*$B$6</f>
+        <v/>
+      </c>
+      <c r="O24" s="103">
+        <f>O22*$B$5+O23*$B$6</f>
+        <v/>
+      </c>
+      <c r="P24" s="103">
+        <f>P22*$B$5+P23*$B$6</f>
+        <v/>
+      </c>
+      <c r="Q24" s="103">
+        <f>Q22*$B$5+Q23*$B$6</f>
+        <v/>
+      </c>
+      <c r="R24" s="103">
+        <f>R22*$B$5+R23*$B$6</f>
+        <v/>
+      </c>
+      <c r="S24" s="103">
+        <f>S22*$B$5+S23*$B$6</f>
+        <v/>
+      </c>
+      <c r="T24" s="103">
+        <f>T22*$B$5+T23*$B$6</f>
+        <v/>
+      </c>
+      <c r="U24" s="103">
+        <f>U22*$B$5+U23*$B$6</f>
+        <v/>
+      </c>
+      <c r="V24" s="103">
+        <f>V22*$B$5+V23*$B$6</f>
+        <v/>
+      </c>
+      <c r="W24" s="103">
+        <f>W22*$B$5+W23*$B$6</f>
+        <v/>
+      </c>
+      <c r="X24" s="103">
+        <f>X22*$B$5+X23*$B$6</f>
+        <v/>
+      </c>
+      <c r="Y24" s="103">
+        <f>Y22*$B$5+Y23*$B$6</f>
+        <v/>
+      </c>
+      <c r="Z24" s="103">
+        <f>Z22*$B$5+Z23*$B$6</f>
+        <v/>
+      </c>
+      <c r="AA24" s="103">
+        <f>AA22*$B$5+AA23*$B$6</f>
+        <v/>
+      </c>
+      <c r="AB24" s="103">
+        <f>AB22*$B$5+AB23*$B$6</f>
+        <v/>
+      </c>
+      <c r="AC24" s="103">
+        <f>AC22*$B$5+AC23*$B$6</f>
+        <v/>
+      </c>
+      <c r="AD24" s="103">
+        <f>AD22*$B$5+AD23*$B$6</f>
+        <v/>
+      </c>
+      <c r="AE24" s="103">
+        <f>AE22*$B$5+AE23*$B$6</f>
+        <v/>
+      </c>
+      <c r="AF24" s="103">
+        <f>AF22*$B$5+AF23*$B$6</f>
+        <v/>
+      </c>
+      <c r="AG24" s="103">
+        <f>AG22*$B$5+AG23*$B$6</f>
+        <v/>
+      </c>
+      <c r="AH24" s="103">
+        <f>AH22*$B$5+AH23*$B$6</f>
+        <v/>
+      </c>
+      <c r="AI24" s="103">
+        <f>AI22*$B$5+AI23*$B$6</f>
+        <v/>
+      </c>
+      <c r="AJ24" s="103">
+        <f>AJ22*$B$5+AJ23*$B$6</f>
+        <v/>
+      </c>
+      <c r="AK24" s="103">
+        <f>AK22*$B$5+AK23*$B$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="45" t="inlineStr">
+        <is>
+          <t>Cohort run month (1 if cohort runs)</t>
+        </is>
+      </c>
+      <c r="B25" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q25" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="W25" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z25" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC25" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF25" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI25" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="101" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="102" t="inlineStr">
+        <is>
+          <t>Cohort seats sold this month</t>
+        </is>
+      </c>
+      <c r="B26" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="101" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="101" t="n">
         <v>5</v>
       </c>
-      <c r="C14" s="95" t="n">
+      <c r="H26" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="101" t="n">
+        <v>7</v>
+      </c>
+      <c r="K26" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="101" t="n">
+        <v>8</v>
+      </c>
+      <c r="N26" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="101" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q26" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="101" t="n">
+        <v>9</v>
+      </c>
+      <c r="T26" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="101" t="n">
         <v>10</v>
       </c>
-      <c r="D14" s="95" t="n">
-        <v>30</v>
-      </c>
-      <c r="E14" s="95" t="n">
-        <v>25</v>
-      </c>
-      <c r="F14" s="95" t="n">
-        <v>30</v>
-      </c>
-      <c r="G14" s="95" t="n">
-        <v>50</v>
-      </c>
-      <c r="H14" s="95" t="n">
-        <v>35</v>
-      </c>
-      <c r="I14" s="95" t="n">
-        <v>35</v>
-      </c>
-      <c r="J14" s="95" t="n">
-        <v>60</v>
-      </c>
-      <c r="K14" s="95" t="n">
-        <v>45</v>
-      </c>
-      <c r="L14" s="95" t="n">
-        <v>50</v>
-      </c>
-      <c r="M14" s="95" t="n">
-        <v>70</v>
-      </c>
-      <c r="N14" s="95" t="n">
-        <v>75</v>
-      </c>
-      <c r="O14" s="95" t="n">
-        <v>80</v>
-      </c>
-      <c r="P14" s="95" t="n">
-        <v>95</v>
-      </c>
-      <c r="Q14" s="95" t="n">
-        <v>85</v>
-      </c>
-      <c r="R14" s="95" t="n">
-        <v>90</v>
-      </c>
-      <c r="S14" s="95" t="n">
-        <v>105</v>
-      </c>
-      <c r="T14" s="95" t="n">
-        <v>95</v>
-      </c>
-      <c r="U14" s="95" t="n">
-        <v>95</v>
-      </c>
-      <c r="V14" s="95" t="n">
-        <v>115</v>
-      </c>
-      <c r="W14" s="95" t="n">
-        <v>105</v>
-      </c>
-      <c r="X14" s="95" t="n">
-        <v>110</v>
-      </c>
-      <c r="Y14" s="95" t="n">
-        <v>125</v>
-      </c>
-      <c r="Z14" s="95" t="n">
-        <v>130</v>
-      </c>
-      <c r="AA14" s="95" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB14" s="95" t="n">
-        <v>150</v>
-      </c>
-      <c r="AC14" s="95" t="n">
-        <v>140</v>
-      </c>
-      <c r="AD14" s="95" t="n">
-        <v>145</v>
-      </c>
-      <c r="AE14" s="95" t="n">
-        <v>160</v>
-      </c>
-      <c r="AF14" s="95" t="n">
-        <v>150</v>
-      </c>
-      <c r="AG14" s="95" t="n">
-        <v>150</v>
-      </c>
-      <c r="AH14" s="95" t="n">
-        <v>170</v>
-      </c>
-      <c r="AI14" s="95" t="n">
-        <v>160</v>
-      </c>
-      <c r="AJ14" s="95" t="n">
-        <v>165</v>
-      </c>
-      <c r="AK14" s="95" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="92" t="inlineStr">
-        <is>
-          <t>Email list size</t>
-        </is>
-      </c>
-      <c r="B15" s="99">
-        <f>B14</f>
-        <v/>
-      </c>
-      <c r="C15" s="99">
-        <f>B15*(1-$B$2)+C14</f>
-        <v/>
-      </c>
-      <c r="D15" s="99">
-        <f>C15*(1-$B$2)+D14</f>
-        <v/>
-      </c>
-      <c r="E15" s="99">
-        <f>D15*(1-$B$2)+E14</f>
-        <v/>
-      </c>
-      <c r="F15" s="99">
-        <f>E15*(1-$B$2)+F14</f>
-        <v/>
-      </c>
-      <c r="G15" s="99">
-        <f>F15*(1-$B$2)+G14</f>
-        <v/>
-      </c>
-      <c r="H15" s="99">
-        <f>G15*(1-$B$2)+H14</f>
-        <v/>
-      </c>
-      <c r="I15" s="99">
-        <f>H15*(1-$B$2)+I14</f>
-        <v/>
-      </c>
-      <c r="J15" s="99">
-        <f>I15*(1-$B$2)+J14</f>
-        <v/>
-      </c>
-      <c r="K15" s="99">
-        <f>J15*(1-$B$2)+K14</f>
-        <v/>
-      </c>
-      <c r="L15" s="99">
-        <f>K15*(1-$B$2)+L14</f>
-        <v/>
-      </c>
-      <c r="M15" s="99">
-        <f>L15*(1-$B$2)+M14</f>
-        <v/>
-      </c>
-      <c r="N15" s="99">
-        <f>M15*(1-$B$2)+N14</f>
-        <v/>
-      </c>
-      <c r="O15" s="99">
-        <f>N15*(1-$B$2)+O14</f>
-        <v/>
-      </c>
-      <c r="P15" s="99">
-        <f>O15*(1-$B$2)+P14</f>
-        <v/>
-      </c>
-      <c r="Q15" s="99">
-        <f>P15*(1-$B$2)+Q14</f>
-        <v/>
-      </c>
-      <c r="R15" s="99">
-        <f>Q15*(1-$B$2)+R14</f>
-        <v/>
-      </c>
-      <c r="S15" s="99">
-        <f>R15*(1-$B$2)+S14</f>
-        <v/>
-      </c>
-      <c r="T15" s="99">
-        <f>S15*(1-$B$2)+T14</f>
-        <v/>
-      </c>
-      <c r="U15" s="99">
-        <f>T15*(1-$B$2)+U14</f>
-        <v/>
-      </c>
-      <c r="V15" s="99">
-        <f>U15*(1-$B$2)+V14</f>
-        <v/>
-      </c>
-      <c r="W15" s="99">
-        <f>V15*(1-$B$2)+W14</f>
-        <v/>
-      </c>
-      <c r="X15" s="99">
-        <f>W15*(1-$B$2)+X14</f>
-        <v/>
-      </c>
-      <c r="Y15" s="99">
-        <f>X15*(1-$B$2)+Y14</f>
-        <v/>
-      </c>
-      <c r="Z15" s="99">
-        <f>Y15*(1-$B$2)+Z14</f>
-        <v/>
-      </c>
-      <c r="AA15" s="99">
-        <f>Z15*(1-$B$2)+AA14</f>
-        <v/>
-      </c>
-      <c r="AB15" s="99">
-        <f>AA15*(1-$B$2)+AB14</f>
-        <v/>
-      </c>
-      <c r="AC15" s="99">
-        <f>AB15*(1-$B$2)+AC14</f>
-        <v/>
-      </c>
-      <c r="AD15" s="99">
-        <f>AC15*(1-$B$2)+AD14</f>
-        <v/>
-      </c>
-      <c r="AE15" s="99">
-        <f>AD15*(1-$B$2)+AE14</f>
-        <v/>
-      </c>
-      <c r="AF15" s="99">
-        <f>AE15*(1-$B$2)+AF14</f>
-        <v/>
-      </c>
-      <c r="AG15" s="99">
-        <f>AF15*(1-$B$2)+AG14</f>
-        <v/>
-      </c>
-      <c r="AH15" s="99">
-        <f>AG15*(1-$B$2)+AH14</f>
-        <v/>
-      </c>
-      <c r="AI15" s="99">
-        <f>AH15*(1-$B$2)+AI14</f>
-        <v/>
-      </c>
-      <c r="AJ15" s="99">
-        <f>AI15*(1-$B$2)+AJ14</f>
-        <v/>
-      </c>
-      <c r="AK15" s="99">
-        <f>AJ15*(1-$B$2)+AK14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="92" t="inlineStr">
-        <is>
-          <t>Paid challenge — standard tickets / month</t>
-        </is>
-      </c>
-      <c r="B16" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="95" t="n">
-        <v>25</v>
-      </c>
-      <c r="E16" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="95" t="n">
-        <v>30</v>
-      </c>
-      <c r="H16" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="95" t="n">
-        <v>35</v>
-      </c>
-      <c r="K16" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="95" t="n">
-        <v>40</v>
-      </c>
-      <c r="N16" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" s="95" t="n">
-        <v>45</v>
-      </c>
-      <c r="Q16" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" s="95" t="n">
-        <v>50</v>
-      </c>
-      <c r="T16" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="95" t="n">
-        <v>55</v>
-      </c>
-      <c r="W16" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="95" t="n">
-        <v>60</v>
-      </c>
-      <c r="Z16" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" s="95" t="n">
-        <v>60</v>
-      </c>
-      <c r="AC16" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" s="95" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF16" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" s="95" t="n">
-        <v>70</v>
-      </c>
-      <c r="AI16" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" s="95" t="n">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="92" t="inlineStr">
-        <is>
-          <t>Paid challenge — VIP tickets / month</t>
-        </is>
-      </c>
-      <c r="B17" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="95" t="n">
-        <v>5</v>
-      </c>
-      <c r="E17" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="95" t="n">
-        <v>6</v>
-      </c>
-      <c r="H17" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="95" t="n">
-        <v>7</v>
-      </c>
-      <c r="K17" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="95" t="n">
-        <v>8</v>
-      </c>
-      <c r="N17" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" s="95" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q17" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" s="95" t="n">
+      <c r="W26" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="101" t="n">
         <v>10</v>
       </c>
-      <c r="T17" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="95" t="n">
-        <v>11</v>
-      </c>
-      <c r="W17" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="95" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z17" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" s="95" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC17" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" s="95" t="n">
-        <v>13</v>
-      </c>
-      <c r="AF17" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" s="95" t="n">
-        <v>14</v>
-      </c>
-      <c r="AI17" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" s="95" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="92" t="inlineStr">
-        <is>
-          <t>Challenge revenue</t>
-        </is>
-      </c>
-      <c r="B18" s="100">
-        <f>B16*$B$5+B17*$B$6</f>
-        <v/>
-      </c>
-      <c r="C18" s="100">
-        <f>C16*$B$5+C17*$B$6</f>
-        <v/>
-      </c>
-      <c r="D18" s="100">
-        <f>D16*$B$5+D17*$B$6</f>
-        <v/>
-      </c>
-      <c r="E18" s="100">
-        <f>E16*$B$5+E17*$B$6</f>
-        <v/>
-      </c>
-      <c r="F18" s="100">
-        <f>F16*$B$5+F17*$B$6</f>
-        <v/>
-      </c>
-      <c r="G18" s="100">
-        <f>G16*$B$5+G17*$B$6</f>
-        <v/>
-      </c>
-      <c r="H18" s="100">
-        <f>H16*$B$5+H17*$B$6</f>
-        <v/>
-      </c>
-      <c r="I18" s="100">
-        <f>I16*$B$5+I17*$B$6</f>
-        <v/>
-      </c>
-      <c r="J18" s="100">
-        <f>J16*$B$5+J17*$B$6</f>
-        <v/>
-      </c>
-      <c r="K18" s="100">
-        <f>K16*$B$5+K17*$B$6</f>
-        <v/>
-      </c>
-      <c r="L18" s="100">
-        <f>L16*$B$5+L17*$B$6</f>
-        <v/>
-      </c>
-      <c r="M18" s="100">
-        <f>M16*$B$5+M17*$B$6</f>
-        <v/>
-      </c>
-      <c r="N18" s="100">
-        <f>N16*$B$5+N17*$B$6</f>
-        <v/>
-      </c>
-      <c r="O18" s="100">
-        <f>O16*$B$5+O17*$B$6</f>
-        <v/>
-      </c>
-      <c r="P18" s="100">
-        <f>P16*$B$5+P17*$B$6</f>
-        <v/>
-      </c>
-      <c r="Q18" s="100">
-        <f>Q16*$B$5+Q17*$B$6</f>
-        <v/>
-      </c>
-      <c r="R18" s="100">
-        <f>R16*$B$5+R17*$B$6</f>
-        <v/>
-      </c>
-      <c r="S18" s="100">
-        <f>S16*$B$5+S17*$B$6</f>
-        <v/>
-      </c>
-      <c r="T18" s="100">
-        <f>T16*$B$5+T17*$B$6</f>
-        <v/>
-      </c>
-      <c r="U18" s="100">
-        <f>U16*$B$5+U17*$B$6</f>
-        <v/>
-      </c>
-      <c r="V18" s="100">
-        <f>V16*$B$5+V17*$B$6</f>
-        <v/>
-      </c>
-      <c r="W18" s="100">
-        <f>W16*$B$5+W17*$B$6</f>
-        <v/>
-      </c>
-      <c r="X18" s="100">
-        <f>X16*$B$5+X17*$B$6</f>
-        <v/>
-      </c>
-      <c r="Y18" s="100">
-        <f>Y16*$B$5+Y17*$B$6</f>
-        <v/>
-      </c>
-      <c r="Z18" s="100">
-        <f>Z16*$B$5+Z17*$B$6</f>
-        <v/>
-      </c>
-      <c r="AA18" s="100">
-        <f>AA16*$B$5+AA17*$B$6</f>
-        <v/>
-      </c>
-      <c r="AB18" s="100">
-        <f>AB16*$B$5+AB17*$B$6</f>
-        <v/>
-      </c>
-      <c r="AC18" s="100">
-        <f>AC16*$B$5+AC17*$B$6</f>
-        <v/>
-      </c>
-      <c r="AD18" s="100">
-        <f>AD16*$B$5+AD17*$B$6</f>
-        <v/>
-      </c>
-      <c r="AE18" s="100">
-        <f>AE16*$B$5+AE17*$B$6</f>
-        <v/>
-      </c>
-      <c r="AF18" s="100">
-        <f>AF16*$B$5+AF17*$B$6</f>
-        <v/>
-      </c>
-      <c r="AG18" s="100">
-        <f>AG16*$B$5+AG17*$B$6</f>
-        <v/>
-      </c>
-      <c r="AH18" s="100">
-        <f>AH16*$B$5+AH17*$B$6</f>
-        <v/>
-      </c>
-      <c r="AI18" s="100">
-        <f>AI16*$B$5+AI17*$B$6</f>
-        <v/>
-      </c>
-      <c r="AJ18" s="100">
-        <f>AJ16*$B$5+AJ17*$B$6</f>
-        <v/>
-      </c>
-      <c r="AK18" s="100">
-        <f>AK16*$B$5+AK17*$B$6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="92" t="inlineStr">
-        <is>
-          <t>Cohort run month (0 / 1)</t>
-        </is>
-      </c>
-      <c r="B19" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q19" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="W19" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z19" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC19" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF19" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI19" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ19" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK19" s="95" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="92" t="inlineStr">
-        <is>
-          <t>Cohort revenue</t>
-        </is>
-      </c>
-      <c r="B20" s="100">
-        <f>B19*$B$4*$B$3</f>
-        <v/>
-      </c>
-      <c r="C20" s="100">
-        <f>C19*$B$4*$B$3</f>
-        <v/>
-      </c>
-      <c r="D20" s="100">
-        <f>D19*$B$4*$B$3</f>
-        <v/>
-      </c>
-      <c r="E20" s="100">
-        <f>E19*$B$4*$B$3</f>
-        <v/>
-      </c>
-      <c r="F20" s="100">
-        <f>F19*$B$4*$B$3</f>
-        <v/>
-      </c>
-      <c r="G20" s="100">
-        <f>G19*$B$4*$B$3</f>
-        <v/>
-      </c>
-      <c r="H20" s="100">
-        <f>H19*$B$4*$B$3</f>
-        <v/>
-      </c>
-      <c r="I20" s="100">
-        <f>I19*$B$4*$B$3</f>
-        <v/>
-      </c>
-      <c r="J20" s="100">
-        <f>J19*$B$4*$B$3</f>
-        <v/>
-      </c>
-      <c r="K20" s="100">
-        <f>K19*$B$4*$B$3</f>
-        <v/>
-      </c>
-      <c r="L20" s="100">
-        <f>L19*$B$4*$B$3</f>
-        <v/>
-      </c>
-      <c r="M20" s="100">
-        <f>M19*$B$4*$B$3</f>
-        <v/>
-      </c>
-      <c r="N20" s="100">
-        <f>N19*$B$4*$B$3</f>
-        <v/>
-      </c>
-      <c r="O20" s="100">
-        <f>O19*$B$4*$B$3</f>
-        <v/>
-      </c>
-      <c r="P20" s="100">
-        <f>P19*$B$4*$B$3</f>
-        <v/>
-      </c>
-      <c r="Q20" s="100">
-        <f>Q19*$B$4*$B$3</f>
-        <v/>
-      </c>
-      <c r="R20" s="100">
-        <f>R19*$B$4*$B$3</f>
-        <v/>
-      </c>
-      <c r="S20" s="100">
-        <f>S19*$B$4*$B$3</f>
-        <v/>
-      </c>
-      <c r="T20" s="100">
-        <f>T19*$B$4*$B$3</f>
-        <v/>
-      </c>
-      <c r="U20" s="100">
-        <f>U19*$B$4*$B$3</f>
-        <v/>
-      </c>
-      <c r="V20" s="100">
-        <f>V19*$B$4*$B$3</f>
-        <v/>
-      </c>
-      <c r="W20" s="100">
-        <f>W19*$B$4*$B$3</f>
-        <v/>
-      </c>
-      <c r="X20" s="100">
-        <f>X19*$B$4*$B$3</f>
-        <v/>
-      </c>
-      <c r="Y20" s="100">
-        <f>Y19*$B$4*$B$3</f>
-        <v/>
-      </c>
-      <c r="Z20" s="100">
-        <f>Z19*$B$4*$B$3</f>
-        <v/>
-      </c>
-      <c r="AA20" s="100">
-        <f>AA19*$B$4*$B$3</f>
-        <v/>
-      </c>
-      <c r="AB20" s="100">
-        <f>AB19*$B$4*$B$3</f>
-        <v/>
-      </c>
-      <c r="AC20" s="100">
-        <f>AC19*$B$4*$B$3</f>
-        <v/>
-      </c>
-      <c r="AD20" s="100">
-        <f>AD19*$B$4*$B$3</f>
-        <v/>
-      </c>
-      <c r="AE20" s="100">
-        <f>AE19*$B$4*$B$3</f>
-        <v/>
-      </c>
-      <c r="AF20" s="100">
-        <f>AF19*$B$4*$B$3</f>
-        <v/>
-      </c>
-      <c r="AG20" s="100">
-        <f>AG19*$B$4*$B$3</f>
-        <v/>
-      </c>
-      <c r="AH20" s="100">
-        <f>AH19*$B$4*$B$3</f>
-        <v/>
-      </c>
-      <c r="AI20" s="100">
-        <f>AI19*$B$4*$B$3</f>
-        <v/>
-      </c>
-      <c r="AJ20" s="100">
-        <f>AJ19*$B$4*$B$3</f>
-        <v/>
-      </c>
-      <c r="AK20" s="100">
-        <f>AK19*$B$4*$B$3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="92" t="inlineStr">
+      <c r="Z26" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="101" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC26" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" s="101" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF26" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" s="101" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI26" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" s="101" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="45" t="inlineStr">
+        <is>
+          <t>Cohort lump-sum revenue (this month)</t>
+        </is>
+      </c>
+      <c r="B27" s="103">
+        <f>B26*(1-$B$11)*$B$3</f>
+        <v/>
+      </c>
+      <c r="C27" s="103">
+        <f>C26*(1-$B$11)*$B$3</f>
+        <v/>
+      </c>
+      <c r="D27" s="103">
+        <f>D26*(1-$B$11)*$B$3</f>
+        <v/>
+      </c>
+      <c r="E27" s="103">
+        <f>E26*(1-$B$11)*$B$3</f>
+        <v/>
+      </c>
+      <c r="F27" s="103">
+        <f>F26*(1-$B$11)*$B$3</f>
+        <v/>
+      </c>
+      <c r="G27" s="103">
+        <f>G26*(1-$B$11)*$B$3</f>
+        <v/>
+      </c>
+      <c r="H27" s="103">
+        <f>H26*(1-$B$11)*$B$3</f>
+        <v/>
+      </c>
+      <c r="I27" s="103">
+        <f>I26*(1-$B$11)*$B$3</f>
+        <v/>
+      </c>
+      <c r="J27" s="103">
+        <f>J26*(1-$B$11)*$B$3</f>
+        <v/>
+      </c>
+      <c r="K27" s="103">
+        <f>K26*(1-$B$11)*$B$3</f>
+        <v/>
+      </c>
+      <c r="L27" s="103">
+        <f>L26*(1-$B$11)*$B$3</f>
+        <v/>
+      </c>
+      <c r="M27" s="103">
+        <f>M26*(1-$B$11)*$B$3</f>
+        <v/>
+      </c>
+      <c r="N27" s="103">
+        <f>N26*(1-$B$11)*$B$3</f>
+        <v/>
+      </c>
+      <c r="O27" s="103">
+        <f>O26*(1-$B$11)*$B$3</f>
+        <v/>
+      </c>
+      <c r="P27" s="103">
+        <f>P26*(1-$B$11)*$B$3</f>
+        <v/>
+      </c>
+      <c r="Q27" s="103">
+        <f>Q26*(1-$B$11)*$B$3</f>
+        <v/>
+      </c>
+      <c r="R27" s="103">
+        <f>R26*(1-$B$11)*$B$3</f>
+        <v/>
+      </c>
+      <c r="S27" s="103">
+        <f>S26*(1-$B$11)*$B$3</f>
+        <v/>
+      </c>
+      <c r="T27" s="103">
+        <f>T26*(1-$B$11)*$B$3</f>
+        <v/>
+      </c>
+      <c r="U27" s="103">
+        <f>U26*(1-$B$11)*$B$3</f>
+        <v/>
+      </c>
+      <c r="V27" s="103">
+        <f>V26*(1-$B$11)*$B$3</f>
+        <v/>
+      </c>
+      <c r="W27" s="103">
+        <f>W26*(1-$B$11)*$B$3</f>
+        <v/>
+      </c>
+      <c r="X27" s="103">
+        <f>X26*(1-$B$11)*$B$3</f>
+        <v/>
+      </c>
+      <c r="Y27" s="103">
+        <f>Y26*(1-$B$11)*$B$3</f>
+        <v/>
+      </c>
+      <c r="Z27" s="103">
+        <f>Z26*(1-$B$11)*$B$3</f>
+        <v/>
+      </c>
+      <c r="AA27" s="103">
+        <f>AA26*(1-$B$11)*$B$3</f>
+        <v/>
+      </c>
+      <c r="AB27" s="103">
+        <f>AB26*(1-$B$11)*$B$3</f>
+        <v/>
+      </c>
+      <c r="AC27" s="103">
+        <f>AC26*(1-$B$11)*$B$3</f>
+        <v/>
+      </c>
+      <c r="AD27" s="103">
+        <f>AD26*(1-$B$11)*$B$3</f>
+        <v/>
+      </c>
+      <c r="AE27" s="103">
+        <f>AE26*(1-$B$11)*$B$3</f>
+        <v/>
+      </c>
+      <c r="AF27" s="103">
+        <f>AF26*(1-$B$11)*$B$3</f>
+        <v/>
+      </c>
+      <c r="AG27" s="103">
+        <f>AG26*(1-$B$11)*$B$3</f>
+        <v/>
+      </c>
+      <c r="AH27" s="103">
+        <f>AH26*(1-$B$11)*$B$3</f>
+        <v/>
+      </c>
+      <c r="AI27" s="103">
+        <f>AI26*(1-$B$11)*$B$3</f>
+        <v/>
+      </c>
+      <c r="AJ27" s="103">
+        <f>AJ26*(1-$B$11)*$B$3</f>
+        <v/>
+      </c>
+      <c r="AK27" s="103">
+        <f>AK26*(1-$B$11)*$B$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="45" t="inlineStr">
+        <is>
+          <t>Cohort plan-installment revenue (this month)</t>
+        </is>
+      </c>
+      <c r="B28" s="103">
+        <f>SUMPRODUCT((COLUMN($B$26:B26)&gt;=COLUMN(B26)-$B$12+1)*$B$26:B26)*$B$11*$B$3*(1+$B$13)/$B$12</f>
+        <v/>
+      </c>
+      <c r="C28" s="103">
+        <f>SUMPRODUCT((COLUMN($B$26:C26)&gt;=COLUMN(C26)-$B$12+1)*$B$26:C26)*$B$11*$B$3*(1+$B$13)/$B$12</f>
+        <v/>
+      </c>
+      <c r="D28" s="103">
+        <f>SUMPRODUCT((COLUMN($B$26:D26)&gt;=COLUMN(D26)-$B$12+1)*$B$26:D26)*$B$11*$B$3*(1+$B$13)/$B$12</f>
+        <v/>
+      </c>
+      <c r="E28" s="103">
+        <f>SUMPRODUCT((COLUMN($B$26:E26)&gt;=COLUMN(E26)-$B$12+1)*$B$26:E26)*$B$11*$B$3*(1+$B$13)/$B$12</f>
+        <v/>
+      </c>
+      <c r="F28" s="103">
+        <f>SUMPRODUCT((COLUMN($B$26:F26)&gt;=COLUMN(F26)-$B$12+1)*$B$26:F26)*$B$11*$B$3*(1+$B$13)/$B$12</f>
+        <v/>
+      </c>
+      <c r="G28" s="103">
+        <f>SUMPRODUCT((COLUMN($B$26:G26)&gt;=COLUMN(G26)-$B$12+1)*$B$26:G26)*$B$11*$B$3*(1+$B$13)/$B$12</f>
+        <v/>
+      </c>
+      <c r="H28" s="103">
+        <f>SUMPRODUCT((COLUMN($B$26:H26)&gt;=COLUMN(H26)-$B$12+1)*$B$26:H26)*$B$11*$B$3*(1+$B$13)/$B$12</f>
+        <v/>
+      </c>
+      <c r="I28" s="103">
+        <f>SUMPRODUCT((COLUMN($B$26:I26)&gt;=COLUMN(I26)-$B$12+1)*$B$26:I26)*$B$11*$B$3*(1+$B$13)/$B$12</f>
+        <v/>
+      </c>
+      <c r="J28" s="103">
+        <f>SUMPRODUCT((COLUMN($B$26:J26)&gt;=COLUMN(J26)-$B$12+1)*$B$26:J26)*$B$11*$B$3*(1+$B$13)/$B$12</f>
+        <v/>
+      </c>
+      <c r="K28" s="103">
+        <f>SUMPRODUCT((COLUMN($B$26:K26)&gt;=COLUMN(K26)-$B$12+1)*$B$26:K26)*$B$11*$B$3*(1+$B$13)/$B$12</f>
+        <v/>
+      </c>
+      <c r="L28" s="103">
+        <f>SUMPRODUCT((COLUMN($B$26:L26)&gt;=COLUMN(L26)-$B$12+1)*$B$26:L26)*$B$11*$B$3*(1+$B$13)/$B$12</f>
+        <v/>
+      </c>
+      <c r="M28" s="103">
+        <f>SUMPRODUCT((COLUMN($B$26:M26)&gt;=COLUMN(M26)-$B$12+1)*$B$26:M26)*$B$11*$B$3*(1+$B$13)/$B$12</f>
+        <v/>
+      </c>
+      <c r="N28" s="103">
+        <f>SUMPRODUCT((COLUMN($B$26:N26)&gt;=COLUMN(N26)-$B$12+1)*$B$26:N26)*$B$11*$B$3*(1+$B$13)/$B$12</f>
+        <v/>
+      </c>
+      <c r="O28" s="103">
+        <f>SUMPRODUCT((COLUMN($B$26:O26)&gt;=COLUMN(O26)-$B$12+1)*$B$26:O26)*$B$11*$B$3*(1+$B$13)/$B$12</f>
+        <v/>
+      </c>
+      <c r="P28" s="103">
+        <f>SUMPRODUCT((COLUMN($B$26:P26)&gt;=COLUMN(P26)-$B$12+1)*$B$26:P26)*$B$11*$B$3*(1+$B$13)/$B$12</f>
+        <v/>
+      </c>
+      <c r="Q28" s="103">
+        <f>SUMPRODUCT((COLUMN($B$26:Q26)&gt;=COLUMN(Q26)-$B$12+1)*$B$26:Q26)*$B$11*$B$3*(1+$B$13)/$B$12</f>
+        <v/>
+      </c>
+      <c r="R28" s="103">
+        <f>SUMPRODUCT((COLUMN($B$26:R26)&gt;=COLUMN(R26)-$B$12+1)*$B$26:R26)*$B$11*$B$3*(1+$B$13)/$B$12</f>
+        <v/>
+      </c>
+      <c r="S28" s="103">
+        <f>SUMPRODUCT((COLUMN($B$26:S26)&gt;=COLUMN(S26)-$B$12+1)*$B$26:S26)*$B$11*$B$3*(1+$B$13)/$B$12</f>
+        <v/>
+      </c>
+      <c r="T28" s="103">
+        <f>SUMPRODUCT((COLUMN($B$26:T26)&gt;=COLUMN(T26)-$B$12+1)*$B$26:T26)*$B$11*$B$3*(1+$B$13)/$B$12</f>
+        <v/>
+      </c>
+      <c r="U28" s="103">
+        <f>SUMPRODUCT((COLUMN($B$26:U26)&gt;=COLUMN(U26)-$B$12+1)*$B$26:U26)*$B$11*$B$3*(1+$B$13)/$B$12</f>
+        <v/>
+      </c>
+      <c r="V28" s="103">
+        <f>SUMPRODUCT((COLUMN($B$26:V26)&gt;=COLUMN(V26)-$B$12+1)*$B$26:V26)*$B$11*$B$3*(1+$B$13)/$B$12</f>
+        <v/>
+      </c>
+      <c r="W28" s="103">
+        <f>SUMPRODUCT((COLUMN($B$26:W26)&gt;=COLUMN(W26)-$B$12+1)*$B$26:W26)*$B$11*$B$3*(1+$B$13)/$B$12</f>
+        <v/>
+      </c>
+      <c r="X28" s="103">
+        <f>SUMPRODUCT((COLUMN($B$26:X26)&gt;=COLUMN(X26)-$B$12+1)*$B$26:X26)*$B$11*$B$3*(1+$B$13)/$B$12</f>
+        <v/>
+      </c>
+      <c r="Y28" s="103">
+        <f>SUMPRODUCT((COLUMN($B$26:Y26)&gt;=COLUMN(Y26)-$B$12+1)*$B$26:Y26)*$B$11*$B$3*(1+$B$13)/$B$12</f>
+        <v/>
+      </c>
+      <c r="Z28" s="103">
+        <f>SUMPRODUCT((COLUMN($B$26:Z26)&gt;=COLUMN(Z26)-$B$12+1)*$B$26:Z26)*$B$11*$B$3*(1+$B$13)/$B$12</f>
+        <v/>
+      </c>
+      <c r="AA28" s="103">
+        <f>SUMPRODUCT((COLUMN($B$26:AA26)&gt;=COLUMN(AA26)-$B$12+1)*$B$26:AA26)*$B$11*$B$3*(1+$B$13)/$B$12</f>
+        <v/>
+      </c>
+      <c r="AB28" s="103">
+        <f>SUMPRODUCT((COLUMN($B$26:AB26)&gt;=COLUMN(AB26)-$B$12+1)*$B$26:AB26)*$B$11*$B$3*(1+$B$13)/$B$12</f>
+        <v/>
+      </c>
+      <c r="AC28" s="103">
+        <f>SUMPRODUCT((COLUMN($B$26:AC26)&gt;=COLUMN(AC26)-$B$12+1)*$B$26:AC26)*$B$11*$B$3*(1+$B$13)/$B$12</f>
+        <v/>
+      </c>
+      <c r="AD28" s="103">
+        <f>SUMPRODUCT((COLUMN($B$26:AD26)&gt;=COLUMN(AD26)-$B$12+1)*$B$26:AD26)*$B$11*$B$3*(1+$B$13)/$B$12</f>
+        <v/>
+      </c>
+      <c r="AE28" s="103">
+        <f>SUMPRODUCT((COLUMN($B$26:AE26)&gt;=COLUMN(AE26)-$B$12+1)*$B$26:AE26)*$B$11*$B$3*(1+$B$13)/$B$12</f>
+        <v/>
+      </c>
+      <c r="AF28" s="103">
+        <f>SUMPRODUCT((COLUMN($B$26:AF26)&gt;=COLUMN(AF26)-$B$12+1)*$B$26:AF26)*$B$11*$B$3*(1+$B$13)/$B$12</f>
+        <v/>
+      </c>
+      <c r="AG28" s="103">
+        <f>SUMPRODUCT((COLUMN($B$26:AG26)&gt;=COLUMN(AG26)-$B$12+1)*$B$26:AG26)*$B$11*$B$3*(1+$B$13)/$B$12</f>
+        <v/>
+      </c>
+      <c r="AH28" s="103">
+        <f>SUMPRODUCT((COLUMN($B$26:AH26)&gt;=COLUMN(AH26)-$B$12+1)*$B$26:AH26)*$B$11*$B$3*(1+$B$13)/$B$12</f>
+        <v/>
+      </c>
+      <c r="AI28" s="103">
+        <f>SUMPRODUCT((COLUMN($B$26:AI26)&gt;=COLUMN(AI26)-$B$12+1)*$B$26:AI26)*$B$11*$B$3*(1+$B$13)/$B$12</f>
+        <v/>
+      </c>
+      <c r="AJ28" s="103">
+        <f>SUMPRODUCT((COLUMN($B$26:AJ26)&gt;=COLUMN(AJ26)-$B$12+1)*$B$26:AJ26)*$B$11*$B$3*(1+$B$13)/$B$12</f>
+        <v/>
+      </c>
+      <c r="AK28" s="103">
+        <f>SUMPRODUCT((COLUMN($B$26:AK26)&gt;=COLUMN(AK26)-$B$12+1)*$B$26:AK26)*$B$11*$B$3*(1+$B$13)/$B$12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="45" t="inlineStr">
+        <is>
+          <t>Cohort revenue (lump + plan)</t>
+        </is>
+      </c>
+      <c r="B29" s="103">
+        <f>B27+B28</f>
+        <v/>
+      </c>
+      <c r="C29" s="103">
+        <f>C27+C28</f>
+        <v/>
+      </c>
+      <c r="D29" s="103">
+        <f>D27+D28</f>
+        <v/>
+      </c>
+      <c r="E29" s="103">
+        <f>E27+E28</f>
+        <v/>
+      </c>
+      <c r="F29" s="103">
+        <f>F27+F28</f>
+        <v/>
+      </c>
+      <c r="G29" s="103">
+        <f>G27+G28</f>
+        <v/>
+      </c>
+      <c r="H29" s="103">
+        <f>H27+H28</f>
+        <v/>
+      </c>
+      <c r="I29" s="103">
+        <f>I27+I28</f>
+        <v/>
+      </c>
+      <c r="J29" s="103">
+        <f>J27+J28</f>
+        <v/>
+      </c>
+      <c r="K29" s="103">
+        <f>K27+K28</f>
+        <v/>
+      </c>
+      <c r="L29" s="103">
+        <f>L27+L28</f>
+        <v/>
+      </c>
+      <c r="M29" s="103">
+        <f>M27+M28</f>
+        <v/>
+      </c>
+      <c r="N29" s="103">
+        <f>N27+N28</f>
+        <v/>
+      </c>
+      <c r="O29" s="103">
+        <f>O27+O28</f>
+        <v/>
+      </c>
+      <c r="P29" s="103">
+        <f>P27+P28</f>
+        <v/>
+      </c>
+      <c r="Q29" s="103">
+        <f>Q27+Q28</f>
+        <v/>
+      </c>
+      <c r="R29" s="103">
+        <f>R27+R28</f>
+        <v/>
+      </c>
+      <c r="S29" s="103">
+        <f>S27+S28</f>
+        <v/>
+      </c>
+      <c r="T29" s="103">
+        <f>T27+T28</f>
+        <v/>
+      </c>
+      <c r="U29" s="103">
+        <f>U27+U28</f>
+        <v/>
+      </c>
+      <c r="V29" s="103">
+        <f>V27+V28</f>
+        <v/>
+      </c>
+      <c r="W29" s="103">
+        <f>W27+W28</f>
+        <v/>
+      </c>
+      <c r="X29" s="103">
+        <f>X27+X28</f>
+        <v/>
+      </c>
+      <c r="Y29" s="103">
+        <f>Y27+Y28</f>
+        <v/>
+      </c>
+      <c r="Z29" s="103">
+        <f>Z27+Z28</f>
+        <v/>
+      </c>
+      <c r="AA29" s="103">
+        <f>AA27+AA28</f>
+        <v/>
+      </c>
+      <c r="AB29" s="103">
+        <f>AB27+AB28</f>
+        <v/>
+      </c>
+      <c r="AC29" s="103">
+        <f>AC27+AC28</f>
+        <v/>
+      </c>
+      <c r="AD29" s="103">
+        <f>AD27+AD28</f>
+        <v/>
+      </c>
+      <c r="AE29" s="103">
+        <f>AE27+AE28</f>
+        <v/>
+      </c>
+      <c r="AF29" s="103">
+        <f>AF27+AF28</f>
+        <v/>
+      </c>
+      <c r="AG29" s="103">
+        <f>AG27+AG28</f>
+        <v/>
+      </c>
+      <c r="AH29" s="103">
+        <f>AH27+AH28</f>
+        <v/>
+      </c>
+      <c r="AI29" s="103">
+        <f>AI27+AI28</f>
+        <v/>
+      </c>
+      <c r="AJ29" s="103">
+        <f>AJ27+AJ28</f>
+        <v/>
+      </c>
+      <c r="AK29" s="103">
+        <f>AK27+AK28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="45" t="inlineStr">
         <is>
           <t>New SaaS customers / month</t>
         </is>
       </c>
-      <c r="B21" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" s="95" t="n">
+      <c r="B30" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="N30" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="101" t="n">
         <v>2</v>
       </c>
-      <c r="Q21" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" s="95" t="n">
+      <c r="Q30" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="101" t="n">
         <v>2</v>
       </c>
-      <c r="T21" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="95" t="n">
+      <c r="T30" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="101" t="n">
         <v>2</v>
       </c>
-      <c r="W21" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" s="95" t="n">
+      <c r="W30" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="101" t="n">
         <v>3</v>
       </c>
-      <c r="Z21" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" s="95" t="n">
+      <c r="Z30" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="101" t="n">
         <v>3</v>
       </c>
-      <c r="AC21" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" s="95" t="n">
+      <c r="AC30" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="101" t="n">
         <v>3</v>
       </c>
-      <c r="AF21" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" s="95" t="n">
+      <c r="AF30" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="101" t="n">
         <v>3</v>
       </c>
-      <c r="AI21" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ21" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK21" s="95" t="n">
+      <c r="AI30" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" s="101" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="92" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="45" t="inlineStr">
         <is>
           <t>Total active SaaS customers</t>
         </is>
       </c>
-      <c r="B22" s="99">
-        <f>B21</f>
-        <v/>
-      </c>
-      <c r="C22" s="99">
-        <f>B22*(1-$B$8)^(1/12)+C21</f>
-        <v/>
-      </c>
-      <c r="D22" s="99">
-        <f>C22*(1-$B$8)^(1/12)+D21</f>
-        <v/>
-      </c>
-      <c r="E22" s="99">
-        <f>D22*(1-$B$8)^(1/12)+E21</f>
-        <v/>
-      </c>
-      <c r="F22" s="99">
-        <f>E22*(1-$B$8)^(1/12)+F21</f>
-        <v/>
-      </c>
-      <c r="G22" s="99">
-        <f>F22*(1-$B$8)^(1/12)+G21</f>
-        <v/>
-      </c>
-      <c r="H22" s="99">
-        <f>G22*(1-$B$8)^(1/12)+H21</f>
-        <v/>
-      </c>
-      <c r="I22" s="99">
-        <f>H22*(1-$B$8)^(1/12)+I21</f>
-        <v/>
-      </c>
-      <c r="J22" s="99">
-        <f>I22*(1-$B$8)^(1/12)+J21</f>
-        <v/>
-      </c>
-      <c r="K22" s="99">
-        <f>J22*(1-$B$8)^(1/12)+K21</f>
-        <v/>
-      </c>
-      <c r="L22" s="99">
-        <f>K22*(1-$B$8)^(1/12)+L21</f>
-        <v/>
-      </c>
-      <c r="M22" s="99">
-        <f>L22*(1-$B$8)^(1/12)+M21</f>
-        <v/>
-      </c>
-      <c r="N22" s="99">
-        <f>M22*(1-$B$8)^(1/12)+N21</f>
-        <v/>
-      </c>
-      <c r="O22" s="99">
-        <f>N22*(1-$B$8)^(1/12)+O21</f>
-        <v/>
-      </c>
-      <c r="P22" s="99">
-        <f>O22*(1-$B$8)^(1/12)+P21</f>
-        <v/>
-      </c>
-      <c r="Q22" s="99">
-        <f>P22*(1-$B$8)^(1/12)+Q21</f>
-        <v/>
-      </c>
-      <c r="R22" s="99">
-        <f>Q22*(1-$B$8)^(1/12)+R21</f>
-        <v/>
-      </c>
-      <c r="S22" s="99">
-        <f>R22*(1-$B$8)^(1/12)+S21</f>
-        <v/>
-      </c>
-      <c r="T22" s="99">
-        <f>S22*(1-$B$8)^(1/12)+T21</f>
-        <v/>
-      </c>
-      <c r="U22" s="99">
-        <f>T22*(1-$B$8)^(1/12)+U21</f>
-        <v/>
-      </c>
-      <c r="V22" s="99">
-        <f>U22*(1-$B$8)^(1/12)+V21</f>
-        <v/>
-      </c>
-      <c r="W22" s="99">
-        <f>V22*(1-$B$8)^(1/12)+W21</f>
-        <v/>
-      </c>
-      <c r="X22" s="99">
-        <f>W22*(1-$B$8)^(1/12)+X21</f>
-        <v/>
-      </c>
-      <c r="Y22" s="99">
-        <f>X22*(1-$B$8)^(1/12)+Y21</f>
-        <v/>
-      </c>
-      <c r="Z22" s="99">
-        <f>Y22*(1-$B$8)^(1/12)+Z21</f>
-        <v/>
-      </c>
-      <c r="AA22" s="99">
-        <f>Z22*(1-$B$8)^(1/12)+AA21</f>
-        <v/>
-      </c>
-      <c r="AB22" s="99">
-        <f>AA22*(1-$B$8)^(1/12)+AB21</f>
-        <v/>
-      </c>
-      <c r="AC22" s="99">
-        <f>AB22*(1-$B$8)^(1/12)+AC21</f>
-        <v/>
-      </c>
-      <c r="AD22" s="99">
-        <f>AC22*(1-$B$8)^(1/12)+AD21</f>
-        <v/>
-      </c>
-      <c r="AE22" s="99">
-        <f>AD22*(1-$B$8)^(1/12)+AE21</f>
-        <v/>
-      </c>
-      <c r="AF22" s="99">
-        <f>AE22*(1-$B$8)^(1/12)+AF21</f>
-        <v/>
-      </c>
-      <c r="AG22" s="99">
-        <f>AF22*(1-$B$8)^(1/12)+AG21</f>
-        <v/>
-      </c>
-      <c r="AH22" s="99">
-        <f>AG22*(1-$B$8)^(1/12)+AH21</f>
-        <v/>
-      </c>
-      <c r="AI22" s="99">
-        <f>AH22*(1-$B$8)^(1/12)+AI21</f>
-        <v/>
-      </c>
-      <c r="AJ22" s="99">
-        <f>AI22*(1-$B$8)^(1/12)+AJ21</f>
-        <v/>
-      </c>
-      <c r="AK22" s="99">
-        <f>AJ22*(1-$B$8)^(1/12)+AK21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="92" t="inlineStr">
+      <c r="B31" s="103">
+        <f>B30</f>
+        <v/>
+      </c>
+      <c r="C31" s="103">
+        <f>B31*(1-$B$8)^(1/12)+C30</f>
+        <v/>
+      </c>
+      <c r="D31" s="103">
+        <f>C31*(1-$B$8)^(1/12)+D30</f>
+        <v/>
+      </c>
+      <c r="E31" s="103">
+        <f>D31*(1-$B$8)^(1/12)+E30</f>
+        <v/>
+      </c>
+      <c r="F31" s="103">
+        <f>E31*(1-$B$8)^(1/12)+F30</f>
+        <v/>
+      </c>
+      <c r="G31" s="103">
+        <f>F31*(1-$B$8)^(1/12)+G30</f>
+        <v/>
+      </c>
+      <c r="H31" s="103">
+        <f>G31*(1-$B$8)^(1/12)+H30</f>
+        <v/>
+      </c>
+      <c r="I31" s="103">
+        <f>H31*(1-$B$8)^(1/12)+I30</f>
+        <v/>
+      </c>
+      <c r="J31" s="103">
+        <f>I31*(1-$B$8)^(1/12)+J30</f>
+        <v/>
+      </c>
+      <c r="K31" s="103">
+        <f>J31*(1-$B$8)^(1/12)+K30</f>
+        <v/>
+      </c>
+      <c r="L31" s="103">
+        <f>K31*(1-$B$8)^(1/12)+L30</f>
+        <v/>
+      </c>
+      <c r="M31" s="103">
+        <f>L31*(1-$B$8)^(1/12)+M30</f>
+        <v/>
+      </c>
+      <c r="N31" s="103">
+        <f>M31*(1-$B$8)^(1/12)+N30</f>
+        <v/>
+      </c>
+      <c r="O31" s="103">
+        <f>N31*(1-$B$8)^(1/12)+O30</f>
+        <v/>
+      </c>
+      <c r="P31" s="103">
+        <f>O31*(1-$B$8)^(1/12)+P30</f>
+        <v/>
+      </c>
+      <c r="Q31" s="103">
+        <f>P31*(1-$B$8)^(1/12)+Q30</f>
+        <v/>
+      </c>
+      <c r="R31" s="103">
+        <f>Q31*(1-$B$8)^(1/12)+R30</f>
+        <v/>
+      </c>
+      <c r="S31" s="103">
+        <f>R31*(1-$B$8)^(1/12)+S30</f>
+        <v/>
+      </c>
+      <c r="T31" s="103">
+        <f>S31*(1-$B$8)^(1/12)+T30</f>
+        <v/>
+      </c>
+      <c r="U31" s="103">
+        <f>T31*(1-$B$8)^(1/12)+U30</f>
+        <v/>
+      </c>
+      <c r="V31" s="103">
+        <f>U31*(1-$B$8)^(1/12)+V30</f>
+        <v/>
+      </c>
+      <c r="W31" s="103">
+        <f>V31*(1-$B$8)^(1/12)+W30</f>
+        <v/>
+      </c>
+      <c r="X31" s="103">
+        <f>W31*(1-$B$8)^(1/12)+X30</f>
+        <v/>
+      </c>
+      <c r="Y31" s="103">
+        <f>X31*(1-$B$8)^(1/12)+Y30</f>
+        <v/>
+      </c>
+      <c r="Z31" s="103">
+        <f>Y31*(1-$B$8)^(1/12)+Z30</f>
+        <v/>
+      </c>
+      <c r="AA31" s="103">
+        <f>Z31*(1-$B$8)^(1/12)+AA30</f>
+        <v/>
+      </c>
+      <c r="AB31" s="103">
+        <f>AA31*(1-$B$8)^(1/12)+AB30</f>
+        <v/>
+      </c>
+      <c r="AC31" s="103">
+        <f>AB31*(1-$B$8)^(1/12)+AC30</f>
+        <v/>
+      </c>
+      <c r="AD31" s="103">
+        <f>AC31*(1-$B$8)^(1/12)+AD30</f>
+        <v/>
+      </c>
+      <c r="AE31" s="103">
+        <f>AD31*(1-$B$8)^(1/12)+AE30</f>
+        <v/>
+      </c>
+      <c r="AF31" s="103">
+        <f>AE31*(1-$B$8)^(1/12)+AF30</f>
+        <v/>
+      </c>
+      <c r="AG31" s="103">
+        <f>AF31*(1-$B$8)^(1/12)+AG30</f>
+        <v/>
+      </c>
+      <c r="AH31" s="103">
+        <f>AG31*(1-$B$8)^(1/12)+AH30</f>
+        <v/>
+      </c>
+      <c r="AI31" s="103">
+        <f>AH31*(1-$B$8)^(1/12)+AI30</f>
+        <v/>
+      </c>
+      <c r="AJ31" s="103">
+        <f>AI31*(1-$B$8)^(1/12)+AJ30</f>
+        <v/>
+      </c>
+      <c r="AK31" s="103">
+        <f>AJ31*(1-$B$8)^(1/12)+AK30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="45" t="inlineStr">
         <is>
           <t>SaaS revenue (monthly recognition)</t>
         </is>
       </c>
-      <c r="B23" s="100">
-        <f>B22*$B$7/12</f>
-        <v/>
-      </c>
-      <c r="C23" s="100">
-        <f>C22*$B$7/12</f>
-        <v/>
-      </c>
-      <c r="D23" s="100">
-        <f>D22*$B$7/12</f>
-        <v/>
-      </c>
-      <c r="E23" s="100">
-        <f>E22*$B$7/12</f>
-        <v/>
-      </c>
-      <c r="F23" s="100">
-        <f>F22*$B$7/12</f>
-        <v/>
-      </c>
-      <c r="G23" s="100">
-        <f>G22*$B$7/12</f>
-        <v/>
-      </c>
-      <c r="H23" s="100">
-        <f>H22*$B$7/12</f>
-        <v/>
-      </c>
-      <c r="I23" s="100">
-        <f>I22*$B$7/12</f>
-        <v/>
-      </c>
-      <c r="J23" s="100">
-        <f>J22*$B$7/12</f>
-        <v/>
-      </c>
-      <c r="K23" s="100">
-        <f>K22*$B$7/12</f>
-        <v/>
-      </c>
-      <c r="L23" s="100">
-        <f>L22*$B$7/12</f>
-        <v/>
-      </c>
-      <c r="M23" s="100">
-        <f>M22*$B$7/12</f>
-        <v/>
-      </c>
-      <c r="N23" s="100">
-        <f>N22*$B$7/12</f>
-        <v/>
-      </c>
-      <c r="O23" s="100">
-        <f>O22*$B$7/12</f>
-        <v/>
-      </c>
-      <c r="P23" s="100">
-        <f>P22*$B$7/12</f>
-        <v/>
-      </c>
-      <c r="Q23" s="100">
-        <f>Q22*$B$7/12</f>
-        <v/>
-      </c>
-      <c r="R23" s="100">
-        <f>R22*$B$7/12</f>
-        <v/>
-      </c>
-      <c r="S23" s="100">
-        <f>S22*$B$7/12</f>
-        <v/>
-      </c>
-      <c r="T23" s="100">
-        <f>T22*$B$7/12</f>
-        <v/>
-      </c>
-      <c r="U23" s="100">
-        <f>U22*$B$7/12</f>
-        <v/>
-      </c>
-      <c r="V23" s="100">
-        <f>V22*$B$7/12</f>
-        <v/>
-      </c>
-      <c r="W23" s="100">
-        <f>W22*$B$7/12</f>
-        <v/>
-      </c>
-      <c r="X23" s="100">
-        <f>X22*$B$7/12</f>
-        <v/>
-      </c>
-      <c r="Y23" s="100">
-        <f>Y22*$B$7/12</f>
-        <v/>
-      </c>
-      <c r="Z23" s="100">
-        <f>Z22*$B$7/12</f>
-        <v/>
-      </c>
-      <c r="AA23" s="100">
-        <f>AA22*$B$7/12</f>
-        <v/>
-      </c>
-      <c r="AB23" s="100">
-        <f>AB22*$B$7/12</f>
-        <v/>
-      </c>
-      <c r="AC23" s="100">
-        <f>AC22*$B$7/12</f>
-        <v/>
-      </c>
-      <c r="AD23" s="100">
-        <f>AD22*$B$7/12</f>
-        <v/>
-      </c>
-      <c r="AE23" s="100">
-        <f>AE22*$B$7/12</f>
-        <v/>
-      </c>
-      <c r="AF23" s="100">
-        <f>AF22*$B$7/12</f>
-        <v/>
-      </c>
-      <c r="AG23" s="100">
-        <f>AG22*$B$7/12</f>
-        <v/>
-      </c>
-      <c r="AH23" s="100">
-        <f>AH22*$B$7/12</f>
-        <v/>
-      </c>
-      <c r="AI23" s="100">
-        <f>AI22*$B$7/12</f>
-        <v/>
-      </c>
-      <c r="AJ23" s="100">
-        <f>AJ22*$B$7/12</f>
-        <v/>
-      </c>
-      <c r="AK23" s="100">
-        <f>AK22*$B$7/12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="90" t="inlineStr">
+      <c r="B32" s="103">
+        <f>B31*$B$7/12</f>
+        <v/>
+      </c>
+      <c r="C32" s="103">
+        <f>C31*$B$7/12</f>
+        <v/>
+      </c>
+      <c r="D32" s="103">
+        <f>D31*$B$7/12</f>
+        <v/>
+      </c>
+      <c r="E32" s="103">
+        <f>E31*$B$7/12</f>
+        <v/>
+      </c>
+      <c r="F32" s="103">
+        <f>F31*$B$7/12</f>
+        <v/>
+      </c>
+      <c r="G32" s="103">
+        <f>G31*$B$7/12</f>
+        <v/>
+      </c>
+      <c r="H32" s="103">
+        <f>H31*$B$7/12</f>
+        <v/>
+      </c>
+      <c r="I32" s="103">
+        <f>I31*$B$7/12</f>
+        <v/>
+      </c>
+      <c r="J32" s="103">
+        <f>J31*$B$7/12</f>
+        <v/>
+      </c>
+      <c r="K32" s="103">
+        <f>K31*$B$7/12</f>
+        <v/>
+      </c>
+      <c r="L32" s="103">
+        <f>L31*$B$7/12</f>
+        <v/>
+      </c>
+      <c r="M32" s="103">
+        <f>M31*$B$7/12</f>
+        <v/>
+      </c>
+      <c r="N32" s="103">
+        <f>N31*$B$7/12</f>
+        <v/>
+      </c>
+      <c r="O32" s="103">
+        <f>O31*$B$7/12</f>
+        <v/>
+      </c>
+      <c r="P32" s="103">
+        <f>P31*$B$7/12</f>
+        <v/>
+      </c>
+      <c r="Q32" s="103">
+        <f>Q31*$B$7/12</f>
+        <v/>
+      </c>
+      <c r="R32" s="103">
+        <f>R31*$B$7/12</f>
+        <v/>
+      </c>
+      <c r="S32" s="103">
+        <f>S31*$B$7/12</f>
+        <v/>
+      </c>
+      <c r="T32" s="103">
+        <f>T31*$B$7/12</f>
+        <v/>
+      </c>
+      <c r="U32" s="103">
+        <f>U31*$B$7/12</f>
+        <v/>
+      </c>
+      <c r="V32" s="103">
+        <f>V31*$B$7/12</f>
+        <v/>
+      </c>
+      <c r="W32" s="103">
+        <f>W31*$B$7/12</f>
+        <v/>
+      </c>
+      <c r="X32" s="103">
+        <f>X31*$B$7/12</f>
+        <v/>
+      </c>
+      <c r="Y32" s="103">
+        <f>Y31*$B$7/12</f>
+        <v/>
+      </c>
+      <c r="Z32" s="103">
+        <f>Z31*$B$7/12</f>
+        <v/>
+      </c>
+      <c r="AA32" s="103">
+        <f>AA31*$B$7/12</f>
+        <v/>
+      </c>
+      <c r="AB32" s="103">
+        <f>AB31*$B$7/12</f>
+        <v/>
+      </c>
+      <c r="AC32" s="103">
+        <f>AC31*$B$7/12</f>
+        <v/>
+      </c>
+      <c r="AD32" s="103">
+        <f>AD31*$B$7/12</f>
+        <v/>
+      </c>
+      <c r="AE32" s="103">
+        <f>AE31*$B$7/12</f>
+        <v/>
+      </c>
+      <c r="AF32" s="103">
+        <f>AF31*$B$7/12</f>
+        <v/>
+      </c>
+      <c r="AG32" s="103">
+        <f>AG31*$B$7/12</f>
+        <v/>
+      </c>
+      <c r="AH32" s="103">
+        <f>AH31*$B$7/12</f>
+        <v/>
+      </c>
+      <c r="AI32" s="103">
+        <f>AI31*$B$7/12</f>
+        <v/>
+      </c>
+      <c r="AJ32" s="103">
+        <f>AJ31*$B$7/12</f>
+        <v/>
+      </c>
+      <c r="AK32" s="103">
+        <f>AK31*$B$7/12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="102" t="inlineStr">
         <is>
           <t>TOTAL REVENUE</t>
         </is>
       </c>
-      <c r="B24" s="100">
-        <f>B18+B20+B23</f>
-        <v/>
-      </c>
-      <c r="C24" s="100">
-        <f>C18+C20+C23</f>
-        <v/>
-      </c>
-      <c r="D24" s="100">
-        <f>D18+D20+D23</f>
-        <v/>
-      </c>
-      <c r="E24" s="100">
-        <f>E18+E20+E23</f>
-        <v/>
-      </c>
-      <c r="F24" s="100">
-        <f>F18+F20+F23</f>
-        <v/>
-      </c>
-      <c r="G24" s="100">
-        <f>G18+G20+G23</f>
-        <v/>
-      </c>
-      <c r="H24" s="100">
-        <f>H18+H20+H23</f>
-        <v/>
-      </c>
-      <c r="I24" s="100">
-        <f>I18+I20+I23</f>
-        <v/>
-      </c>
-      <c r="J24" s="100">
-        <f>J18+J20+J23</f>
-        <v/>
-      </c>
-      <c r="K24" s="100">
-        <f>K18+K20+K23</f>
-        <v/>
-      </c>
-      <c r="L24" s="100">
-        <f>L18+L20+L23</f>
-        <v/>
-      </c>
-      <c r="M24" s="100">
-        <f>M18+M20+M23</f>
-        <v/>
-      </c>
-      <c r="N24" s="100">
-        <f>N18+N20+N23</f>
-        <v/>
-      </c>
-      <c r="O24" s="100">
-        <f>O18+O20+O23</f>
-        <v/>
-      </c>
-      <c r="P24" s="100">
-        <f>P18+P20+P23</f>
-        <v/>
-      </c>
-      <c r="Q24" s="100">
-        <f>Q18+Q20+Q23</f>
-        <v/>
-      </c>
-      <c r="R24" s="100">
-        <f>R18+R20+R23</f>
-        <v/>
-      </c>
-      <c r="S24" s="100">
-        <f>S18+S20+S23</f>
-        <v/>
-      </c>
-      <c r="T24" s="100">
-        <f>T18+T20+T23</f>
-        <v/>
-      </c>
-      <c r="U24" s="100">
-        <f>U18+U20+U23</f>
-        <v/>
-      </c>
-      <c r="V24" s="100">
-        <f>V18+V20+V23</f>
-        <v/>
-      </c>
-      <c r="W24" s="100">
-        <f>W18+W20+W23</f>
-        <v/>
-      </c>
-      <c r="X24" s="100">
-        <f>X18+X20+X23</f>
-        <v/>
-      </c>
-      <c r="Y24" s="100">
-        <f>Y18+Y20+Y23</f>
-        <v/>
-      </c>
-      <c r="Z24" s="100">
-        <f>Z18+Z20+Z23</f>
-        <v/>
-      </c>
-      <c r="AA24" s="100">
-        <f>AA18+AA20+AA23</f>
-        <v/>
-      </c>
-      <c r="AB24" s="100">
-        <f>AB18+AB20+AB23</f>
-        <v/>
-      </c>
-      <c r="AC24" s="100">
-        <f>AC18+AC20+AC23</f>
-        <v/>
-      </c>
-      <c r="AD24" s="100">
-        <f>AD18+AD20+AD23</f>
-        <v/>
-      </c>
-      <c r="AE24" s="100">
-        <f>AE18+AE20+AE23</f>
-        <v/>
-      </c>
-      <c r="AF24" s="100">
-        <f>AF18+AF20+AF23</f>
-        <v/>
-      </c>
-      <c r="AG24" s="100">
-        <f>AG18+AG20+AG23</f>
-        <v/>
-      </c>
-      <c r="AH24" s="100">
-        <f>AH18+AH20+AH23</f>
-        <v/>
-      </c>
-      <c r="AI24" s="100">
-        <f>AI18+AI20+AI23</f>
-        <v/>
-      </c>
-      <c r="AJ24" s="100">
-        <f>AJ18+AJ20+AJ23</f>
-        <v/>
-      </c>
-      <c r="AK24" s="100">
-        <f>AK18+AK20+AK23</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="92" t="inlineStr">
+      <c r="B33" s="103">
+        <f>B24+B29+B32</f>
+        <v/>
+      </c>
+      <c r="C33" s="103">
+        <f>C24+C29+C32</f>
+        <v/>
+      </c>
+      <c r="D33" s="103">
+        <f>D24+D29+D32</f>
+        <v/>
+      </c>
+      <c r="E33" s="103">
+        <f>E24+E29+E32</f>
+        <v/>
+      </c>
+      <c r="F33" s="103">
+        <f>F24+F29+F32</f>
+        <v/>
+      </c>
+      <c r="G33" s="103">
+        <f>G24+G29+G32</f>
+        <v/>
+      </c>
+      <c r="H33" s="103">
+        <f>H24+H29+H32</f>
+        <v/>
+      </c>
+      <c r="I33" s="103">
+        <f>I24+I29+I32</f>
+        <v/>
+      </c>
+      <c r="J33" s="103">
+        <f>J24+J29+J32</f>
+        <v/>
+      </c>
+      <c r="K33" s="103">
+        <f>K24+K29+K32</f>
+        <v/>
+      </c>
+      <c r="L33" s="103">
+        <f>L24+L29+L32</f>
+        <v/>
+      </c>
+      <c r="M33" s="103">
+        <f>M24+M29+M32</f>
+        <v/>
+      </c>
+      <c r="N33" s="103">
+        <f>N24+N29+N32</f>
+        <v/>
+      </c>
+      <c r="O33" s="103">
+        <f>O24+O29+O32</f>
+        <v/>
+      </c>
+      <c r="P33" s="103">
+        <f>P24+P29+P32</f>
+        <v/>
+      </c>
+      <c r="Q33" s="103">
+        <f>Q24+Q29+Q32</f>
+        <v/>
+      </c>
+      <c r="R33" s="103">
+        <f>R24+R29+R32</f>
+        <v/>
+      </c>
+      <c r="S33" s="103">
+        <f>S24+S29+S32</f>
+        <v/>
+      </c>
+      <c r="T33" s="103">
+        <f>T24+T29+T32</f>
+        <v/>
+      </c>
+      <c r="U33" s="103">
+        <f>U24+U29+U32</f>
+        <v/>
+      </c>
+      <c r="V33" s="103">
+        <f>V24+V29+V32</f>
+        <v/>
+      </c>
+      <c r="W33" s="103">
+        <f>W24+W29+W32</f>
+        <v/>
+      </c>
+      <c r="X33" s="103">
+        <f>X24+X29+X32</f>
+        <v/>
+      </c>
+      <c r="Y33" s="103">
+        <f>Y24+Y29+Y32</f>
+        <v/>
+      </c>
+      <c r="Z33" s="103">
+        <f>Z24+Z29+Z32</f>
+        <v/>
+      </c>
+      <c r="AA33" s="103">
+        <f>AA24+AA29+AA32</f>
+        <v/>
+      </c>
+      <c r="AB33" s="103">
+        <f>AB24+AB29+AB32</f>
+        <v/>
+      </c>
+      <c r="AC33" s="103">
+        <f>AC24+AC29+AC32</f>
+        <v/>
+      </c>
+      <c r="AD33" s="103">
+        <f>AD24+AD29+AD32</f>
+        <v/>
+      </c>
+      <c r="AE33" s="103">
+        <f>AE24+AE29+AE32</f>
+        <v/>
+      </c>
+      <c r="AF33" s="103">
+        <f>AF24+AF29+AF32</f>
+        <v/>
+      </c>
+      <c r="AG33" s="103">
+        <f>AG24+AG29+AG32</f>
+        <v/>
+      </c>
+      <c r="AH33" s="103">
+        <f>AH24+AH29+AH32</f>
+        <v/>
+      </c>
+      <c r="AI33" s="103">
+        <f>AI24+AI29+AI32</f>
+        <v/>
+      </c>
+      <c r="AJ33" s="103">
+        <f>AJ24+AJ29+AJ32</f>
+        <v/>
+      </c>
+      <c r="AK33" s="103">
+        <f>AK24+AK29+AK32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="45" t="inlineStr">
+        <is>
+          <t>Card processing fees (est.)</t>
+        </is>
+      </c>
+      <c r="B34" s="103">
+        <f>B33*$B$14+(B22+B23+B26)*$B$15</f>
+        <v/>
+      </c>
+      <c r="C34" s="103">
+        <f>C33*$B$14+(C22+C23+C26)*$B$15</f>
+        <v/>
+      </c>
+      <c r="D34" s="103">
+        <f>D33*$B$14+(D22+D23+D26)*$B$15</f>
+        <v/>
+      </c>
+      <c r="E34" s="103">
+        <f>E33*$B$14+(E22+E23+E26)*$B$15</f>
+        <v/>
+      </c>
+      <c r="F34" s="103">
+        <f>F33*$B$14+(F22+F23+F26)*$B$15</f>
+        <v/>
+      </c>
+      <c r="G34" s="103">
+        <f>G33*$B$14+(G22+G23+G26)*$B$15</f>
+        <v/>
+      </c>
+      <c r="H34" s="103">
+        <f>H33*$B$14+(H22+H23+H26)*$B$15</f>
+        <v/>
+      </c>
+      <c r="I34" s="103">
+        <f>I33*$B$14+(I22+I23+I26)*$B$15</f>
+        <v/>
+      </c>
+      <c r="J34" s="103">
+        <f>J33*$B$14+(J22+J23+J26)*$B$15</f>
+        <v/>
+      </c>
+      <c r="K34" s="103">
+        <f>K33*$B$14+(K22+K23+K26)*$B$15</f>
+        <v/>
+      </c>
+      <c r="L34" s="103">
+        <f>L33*$B$14+(L22+L23+L26)*$B$15</f>
+        <v/>
+      </c>
+      <c r="M34" s="103">
+        <f>M33*$B$14+(M22+M23+M26)*$B$15</f>
+        <v/>
+      </c>
+      <c r="N34" s="103">
+        <f>N33*$B$14+(N22+N23+N26)*$B$15</f>
+        <v/>
+      </c>
+      <c r="O34" s="103">
+        <f>O33*$B$14+(O22+O23+O26)*$B$15</f>
+        <v/>
+      </c>
+      <c r="P34" s="103">
+        <f>P33*$B$14+(P22+P23+P26)*$B$15</f>
+        <v/>
+      </c>
+      <c r="Q34" s="103">
+        <f>Q33*$B$14+(Q22+Q23+Q26)*$B$15</f>
+        <v/>
+      </c>
+      <c r="R34" s="103">
+        <f>R33*$B$14+(R22+R23+R26)*$B$15</f>
+        <v/>
+      </c>
+      <c r="S34" s="103">
+        <f>S33*$B$14+(S22+S23+S26)*$B$15</f>
+        <v/>
+      </c>
+      <c r="T34" s="103">
+        <f>T33*$B$14+(T22+T23+T26)*$B$15</f>
+        <v/>
+      </c>
+      <c r="U34" s="103">
+        <f>U33*$B$14+(U22+U23+U26)*$B$15</f>
+        <v/>
+      </c>
+      <c r="V34" s="103">
+        <f>V33*$B$14+(V22+V23+V26)*$B$15</f>
+        <v/>
+      </c>
+      <c r="W34" s="103">
+        <f>W33*$B$14+(W22+W23+W26)*$B$15</f>
+        <v/>
+      </c>
+      <c r="X34" s="103">
+        <f>X33*$B$14+(X22+X23+X26)*$B$15</f>
+        <v/>
+      </c>
+      <c r="Y34" s="103">
+        <f>Y33*$B$14+(Y22+Y23+Y26)*$B$15</f>
+        <v/>
+      </c>
+      <c r="Z34" s="103">
+        <f>Z33*$B$14+(Z22+Z23+Z26)*$B$15</f>
+        <v/>
+      </c>
+      <c r="AA34" s="103">
+        <f>AA33*$B$14+(AA22+AA23+AA26)*$B$15</f>
+        <v/>
+      </c>
+      <c r="AB34" s="103">
+        <f>AB33*$B$14+(AB22+AB23+AB26)*$B$15</f>
+        <v/>
+      </c>
+      <c r="AC34" s="103">
+        <f>AC33*$B$14+(AC22+AC23+AC26)*$B$15</f>
+        <v/>
+      </c>
+      <c r="AD34" s="103">
+        <f>AD33*$B$14+(AD22+AD23+AD26)*$B$15</f>
+        <v/>
+      </c>
+      <c r="AE34" s="103">
+        <f>AE33*$B$14+(AE22+AE23+AE26)*$B$15</f>
+        <v/>
+      </c>
+      <c r="AF34" s="103">
+        <f>AF33*$B$14+(AF22+AF23+AF26)*$B$15</f>
+        <v/>
+      </c>
+      <c r="AG34" s="103">
+        <f>AG33*$B$14+(AG22+AG23+AG26)*$B$15</f>
+        <v/>
+      </c>
+      <c r="AH34" s="103">
+        <f>AH33*$B$14+(AH22+AH23+AH26)*$B$15</f>
+        <v/>
+      </c>
+      <c r="AI34" s="103">
+        <f>AI33*$B$14+(AI22+AI23+AI26)*$B$15</f>
+        <v/>
+      </c>
+      <c r="AJ34" s="103">
+        <f>AJ33*$B$14+(AJ22+AJ23+AJ26)*$B$15</f>
+        <v/>
+      </c>
+      <c r="AK34" s="103">
+        <f>AK33*$B$14+(AK22+AK23+AK26)*$B$15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="45" t="inlineStr">
         <is>
           <t>Server units</t>
         </is>
       </c>
-      <c r="B25" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="L25" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="M25" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="N25" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="O25" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="P25" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q25" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="R25" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="S25" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="T25" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="U25" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="V25" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="W25" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="X25" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y25" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z25" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA25" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB25" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC25" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD25" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE25" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF25" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG25" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH25" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI25" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ25" s="95" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK25" s="95" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="92" t="inlineStr">
+      <c r="B35" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="N35" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="P35" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q35" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="R35" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="S35" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="T35" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="V35" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="X35" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y35" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z35" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA35" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB35" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC35" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD35" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE35" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF35" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG35" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH35" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI35" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ35" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK35" s="101" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="45" t="inlineStr">
         <is>
           <t>Infrastructure cost</t>
         </is>
       </c>
-      <c r="B26" s="100">
-        <f>B25*$B$10</f>
-        <v/>
-      </c>
-      <c r="C26" s="100">
-        <f>C25*$B$10</f>
-        <v/>
-      </c>
-      <c r="D26" s="100">
-        <f>D25*$B$10</f>
-        <v/>
-      </c>
-      <c r="E26" s="100">
-        <f>E25*$B$10</f>
-        <v/>
-      </c>
-      <c r="F26" s="100">
-        <f>F25*$B$10</f>
-        <v/>
-      </c>
-      <c r="G26" s="100">
-        <f>G25*$B$10</f>
-        <v/>
-      </c>
-      <c r="H26" s="100">
-        <f>H25*$B$10</f>
-        <v/>
-      </c>
-      <c r="I26" s="100">
-        <f>I25*$B$10</f>
-        <v/>
-      </c>
-      <c r="J26" s="100">
-        <f>J25*$B$10</f>
-        <v/>
-      </c>
-      <c r="K26" s="100">
-        <f>K25*$B$10</f>
-        <v/>
-      </c>
-      <c r="L26" s="100">
-        <f>L25*$B$10</f>
-        <v/>
-      </c>
-      <c r="M26" s="100">
-        <f>M25*$B$10</f>
-        <v/>
-      </c>
-      <c r="N26" s="100">
-        <f>N25*$B$10</f>
-        <v/>
-      </c>
-      <c r="O26" s="100">
-        <f>O25*$B$10</f>
-        <v/>
-      </c>
-      <c r="P26" s="100">
-        <f>P25*$B$10</f>
-        <v/>
-      </c>
-      <c r="Q26" s="100">
-        <f>Q25*$B$10</f>
-        <v/>
-      </c>
-      <c r="R26" s="100">
-        <f>R25*$B$10</f>
-        <v/>
-      </c>
-      <c r="S26" s="100">
-        <f>S25*$B$10</f>
-        <v/>
-      </c>
-      <c r="T26" s="100">
-        <f>T25*$B$10</f>
-        <v/>
-      </c>
-      <c r="U26" s="100">
-        <f>U25*$B$10</f>
-        <v/>
-      </c>
-      <c r="V26" s="100">
-        <f>V25*$B$10</f>
-        <v/>
-      </c>
-      <c r="W26" s="100">
-        <f>W25*$B$10</f>
-        <v/>
-      </c>
-      <c r="X26" s="100">
-        <f>X25*$B$10</f>
-        <v/>
-      </c>
-      <c r="Y26" s="100">
-        <f>Y25*$B$10</f>
-        <v/>
-      </c>
-      <c r="Z26" s="100">
-        <f>Z25*$B$10</f>
-        <v/>
-      </c>
-      <c r="AA26" s="100">
-        <f>AA25*$B$10</f>
-        <v/>
-      </c>
-      <c r="AB26" s="100">
-        <f>AB25*$B$10</f>
-        <v/>
-      </c>
-      <c r="AC26" s="100">
-        <f>AC25*$B$10</f>
-        <v/>
-      </c>
-      <c r="AD26" s="100">
-        <f>AD25*$B$10</f>
-        <v/>
-      </c>
-      <c r="AE26" s="100">
-        <f>AE25*$B$10</f>
-        <v/>
-      </c>
-      <c r="AF26" s="100">
-        <f>AF25*$B$10</f>
-        <v/>
-      </c>
-      <c r="AG26" s="100">
-        <f>AG25*$B$10</f>
-        <v/>
-      </c>
-      <c r="AH26" s="100">
-        <f>AH25*$B$10</f>
-        <v/>
-      </c>
-      <c r="AI26" s="100">
-        <f>AI25*$B$10</f>
-        <v/>
-      </c>
-      <c r="AJ26" s="100">
-        <f>AJ25*$B$10</f>
-        <v/>
-      </c>
-      <c r="AK26" s="100">
-        <f>AK25*$B$10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="92" t="inlineStr">
+      <c r="B36" s="103">
+        <f>B35*$B$10</f>
+        <v/>
+      </c>
+      <c r="C36" s="103">
+        <f>C35*$B$10</f>
+        <v/>
+      </c>
+      <c r="D36" s="103">
+        <f>D35*$B$10</f>
+        <v/>
+      </c>
+      <c r="E36" s="103">
+        <f>E35*$B$10</f>
+        <v/>
+      </c>
+      <c r="F36" s="103">
+        <f>F35*$B$10</f>
+        <v/>
+      </c>
+      <c r="G36" s="103">
+        <f>G35*$B$10</f>
+        <v/>
+      </c>
+      <c r="H36" s="103">
+        <f>H35*$B$10</f>
+        <v/>
+      </c>
+      <c r="I36" s="103">
+        <f>I35*$B$10</f>
+        <v/>
+      </c>
+      <c r="J36" s="103">
+        <f>J35*$B$10</f>
+        <v/>
+      </c>
+      <c r="K36" s="103">
+        <f>K35*$B$10</f>
+        <v/>
+      </c>
+      <c r="L36" s="103">
+        <f>L35*$B$10</f>
+        <v/>
+      </c>
+      <c r="M36" s="103">
+        <f>M35*$B$10</f>
+        <v/>
+      </c>
+      <c r="N36" s="103">
+        <f>N35*$B$10</f>
+        <v/>
+      </c>
+      <c r="O36" s="103">
+        <f>O35*$B$10</f>
+        <v/>
+      </c>
+      <c r="P36" s="103">
+        <f>P35*$B$10</f>
+        <v/>
+      </c>
+      <c r="Q36" s="103">
+        <f>Q35*$B$10</f>
+        <v/>
+      </c>
+      <c r="R36" s="103">
+        <f>R35*$B$10</f>
+        <v/>
+      </c>
+      <c r="S36" s="103">
+        <f>S35*$B$10</f>
+        <v/>
+      </c>
+      <c r="T36" s="103">
+        <f>T35*$B$10</f>
+        <v/>
+      </c>
+      <c r="U36" s="103">
+        <f>U35*$B$10</f>
+        <v/>
+      </c>
+      <c r="V36" s="103">
+        <f>V35*$B$10</f>
+        <v/>
+      </c>
+      <c r="W36" s="103">
+        <f>W35*$B$10</f>
+        <v/>
+      </c>
+      <c r="X36" s="103">
+        <f>X35*$B$10</f>
+        <v/>
+      </c>
+      <c r="Y36" s="103">
+        <f>Y35*$B$10</f>
+        <v/>
+      </c>
+      <c r="Z36" s="103">
+        <f>Z35*$B$10</f>
+        <v/>
+      </c>
+      <c r="AA36" s="103">
+        <f>AA35*$B$10</f>
+        <v/>
+      </c>
+      <c r="AB36" s="103">
+        <f>AB35*$B$10</f>
+        <v/>
+      </c>
+      <c r="AC36" s="103">
+        <f>AC35*$B$10</f>
+        <v/>
+      </c>
+      <c r="AD36" s="103">
+        <f>AD35*$B$10</f>
+        <v/>
+      </c>
+      <c r="AE36" s="103">
+        <f>AE35*$B$10</f>
+        <v/>
+      </c>
+      <c r="AF36" s="103">
+        <f>AF35*$B$10</f>
+        <v/>
+      </c>
+      <c r="AG36" s="103">
+        <f>AG35*$B$10</f>
+        <v/>
+      </c>
+      <c r="AH36" s="103">
+        <f>AH35*$B$10</f>
+        <v/>
+      </c>
+      <c r="AI36" s="103">
+        <f>AI35*$B$10</f>
+        <v/>
+      </c>
+      <c r="AJ36" s="103">
+        <f>AJ35*$B$10</f>
+        <v/>
+      </c>
+      <c r="AK36" s="103">
+        <f>AK35*$B$10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="45" t="inlineStr">
         <is>
           <t>Total expenses</t>
         </is>
       </c>
-      <c r="B27" s="100">
-        <f>$B$9+B26</f>
-        <v/>
-      </c>
-      <c r="C27" s="100">
-        <f>$B$9+C26</f>
-        <v/>
-      </c>
-      <c r="D27" s="100">
-        <f>$B$9+D26</f>
-        <v/>
-      </c>
-      <c r="E27" s="100">
-        <f>$B$9+E26</f>
-        <v/>
-      </c>
-      <c r="F27" s="100">
-        <f>$B$9+F26</f>
-        <v/>
-      </c>
-      <c r="G27" s="100">
-        <f>$B$9+G26</f>
-        <v/>
-      </c>
-      <c r="H27" s="100">
-        <f>$B$9+H26</f>
-        <v/>
-      </c>
-      <c r="I27" s="100">
-        <f>$B$9+I26</f>
-        <v/>
-      </c>
-      <c r="J27" s="100">
-        <f>$B$9+J26</f>
-        <v/>
-      </c>
-      <c r="K27" s="100">
-        <f>$B$9+K26</f>
-        <v/>
-      </c>
-      <c r="L27" s="100">
-        <f>$B$9+L26</f>
-        <v/>
-      </c>
-      <c r="M27" s="100">
-        <f>$B$9+M26</f>
-        <v/>
-      </c>
-      <c r="N27" s="100">
-        <f>$B$9+N26</f>
-        <v/>
-      </c>
-      <c r="O27" s="100">
-        <f>$B$9+O26</f>
-        <v/>
-      </c>
-      <c r="P27" s="100">
-        <f>$B$9+P26</f>
-        <v/>
-      </c>
-      <c r="Q27" s="100">
-        <f>$B$9+Q26</f>
-        <v/>
-      </c>
-      <c r="R27" s="100">
-        <f>$B$9+R26</f>
-        <v/>
-      </c>
-      <c r="S27" s="100">
-        <f>$B$9+S26</f>
-        <v/>
-      </c>
-      <c r="T27" s="100">
-        <f>$B$9+T26</f>
-        <v/>
-      </c>
-      <c r="U27" s="100">
-        <f>$B$9+U26</f>
-        <v/>
-      </c>
-      <c r="V27" s="100">
-        <f>$B$9+V26</f>
-        <v/>
-      </c>
-      <c r="W27" s="100">
-        <f>$B$9+W26</f>
-        <v/>
-      </c>
-      <c r="X27" s="100">
-        <f>$B$9+X26</f>
-        <v/>
-      </c>
-      <c r="Y27" s="100">
-        <f>$B$9+Y26</f>
-        <v/>
-      </c>
-      <c r="Z27" s="100">
-        <f>$B$9+Z26</f>
-        <v/>
-      </c>
-      <c r="AA27" s="100">
-        <f>$B$9+AA26</f>
-        <v/>
-      </c>
-      <c r="AB27" s="100">
-        <f>$B$9+AB26</f>
-        <v/>
-      </c>
-      <c r="AC27" s="100">
-        <f>$B$9+AC26</f>
-        <v/>
-      </c>
-      <c r="AD27" s="100">
-        <f>$B$9+AD26</f>
-        <v/>
-      </c>
-      <c r="AE27" s="100">
-        <f>$B$9+AE26</f>
-        <v/>
-      </c>
-      <c r="AF27" s="100">
-        <f>$B$9+AF26</f>
-        <v/>
-      </c>
-      <c r="AG27" s="100">
-        <f>$B$9+AG26</f>
-        <v/>
-      </c>
-      <c r="AH27" s="100">
-        <f>$B$9+AH26</f>
-        <v/>
-      </c>
-      <c r="AI27" s="100">
-        <f>$B$9+AI26</f>
-        <v/>
-      </c>
-      <c r="AJ27" s="100">
-        <f>$B$9+AJ26</f>
-        <v/>
-      </c>
-      <c r="AK27" s="100">
-        <f>$B$9+AK26</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="90" t="inlineStr">
-        <is>
-          <t>Profit and (Loss)</t>
-        </is>
-      </c>
-      <c r="B28" s="100">
-        <f>B24-B27</f>
-        <v/>
-      </c>
-      <c r="C28" s="100">
-        <f>C24-C27</f>
-        <v/>
-      </c>
-      <c r="D28" s="100">
-        <f>D24-D27</f>
-        <v/>
-      </c>
-      <c r="E28" s="100">
-        <f>E24-E27</f>
-        <v/>
-      </c>
-      <c r="F28" s="100">
-        <f>F24-F27</f>
-        <v/>
-      </c>
-      <c r="G28" s="100">
-        <f>G24-G27</f>
-        <v/>
-      </c>
-      <c r="H28" s="100">
-        <f>H24-H27</f>
-        <v/>
-      </c>
-      <c r="I28" s="100">
-        <f>I24-I27</f>
-        <v/>
-      </c>
-      <c r="J28" s="100">
-        <f>J24-J27</f>
-        <v/>
-      </c>
-      <c r="K28" s="100">
-        <f>K24-K27</f>
-        <v/>
-      </c>
-      <c r="L28" s="100">
-        <f>L24-L27</f>
-        <v/>
-      </c>
-      <c r="M28" s="100">
-        <f>M24-M27</f>
-        <v/>
-      </c>
-      <c r="N28" s="100">
-        <f>N24-N27</f>
-        <v/>
-      </c>
-      <c r="O28" s="100">
-        <f>O24-O27</f>
-        <v/>
-      </c>
-      <c r="P28" s="100">
-        <f>P24-P27</f>
-        <v/>
-      </c>
-      <c r="Q28" s="100">
-        <f>Q24-Q27</f>
-        <v/>
-      </c>
-      <c r="R28" s="100">
-        <f>R24-R27</f>
-        <v/>
-      </c>
-      <c r="S28" s="100">
-        <f>S24-S27</f>
-        <v/>
-      </c>
-      <c r="T28" s="100">
-        <f>T24-T27</f>
-        <v/>
-      </c>
-      <c r="U28" s="100">
-        <f>U24-U27</f>
-        <v/>
-      </c>
-      <c r="V28" s="100">
-        <f>V24-V27</f>
-        <v/>
-      </c>
-      <c r="W28" s="100">
-        <f>W24-W27</f>
-        <v/>
-      </c>
-      <c r="X28" s="100">
-        <f>X24-X27</f>
-        <v/>
-      </c>
-      <c r="Y28" s="100">
-        <f>Y24-Y27</f>
-        <v/>
-      </c>
-      <c r="Z28" s="100">
-        <f>Z24-Z27</f>
-        <v/>
-      </c>
-      <c r="AA28" s="100">
-        <f>AA24-AA27</f>
-        <v/>
-      </c>
-      <c r="AB28" s="100">
-        <f>AB24-AB27</f>
-        <v/>
-      </c>
-      <c r="AC28" s="100">
-        <f>AC24-AC27</f>
-        <v/>
-      </c>
-      <c r="AD28" s="100">
-        <f>AD24-AD27</f>
-        <v/>
-      </c>
-      <c r="AE28" s="100">
-        <f>AE24-AE27</f>
-        <v/>
-      </c>
-      <c r="AF28" s="100">
-        <f>AF24-AF27</f>
-        <v/>
-      </c>
-      <c r="AG28" s="100">
-        <f>AG24-AG27</f>
-        <v/>
-      </c>
-      <c r="AH28" s="100">
-        <f>AH24-AH27</f>
-        <v/>
-      </c>
-      <c r="AI28" s="100">
-        <f>AI24-AI27</f>
-        <v/>
-      </c>
-      <c r="AJ28" s="100">
-        <f>AJ24-AJ27</f>
-        <v/>
-      </c>
-      <c r="AK28" s="100">
-        <f>AK24-AK27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="90" t="inlineStr">
-        <is>
-          <t>Cumulative Profit and (Loss)</t>
-        </is>
-      </c>
-      <c r="B29" s="100">
-        <f>B28</f>
-        <v/>
-      </c>
-      <c r="C29" s="100">
-        <f>B29+C28</f>
-        <v/>
-      </c>
-      <c r="D29" s="100">
-        <f>C29+D28</f>
-        <v/>
-      </c>
-      <c r="E29" s="100">
-        <f>D29+E28</f>
-        <v/>
-      </c>
-      <c r="F29" s="100">
-        <f>E29+F28</f>
-        <v/>
-      </c>
-      <c r="G29" s="100">
-        <f>F29+G28</f>
-        <v/>
-      </c>
-      <c r="H29" s="100">
-        <f>G29+H28</f>
-        <v/>
-      </c>
-      <c r="I29" s="100">
-        <f>H29+I28</f>
-        <v/>
-      </c>
-      <c r="J29" s="100">
-        <f>I29+J28</f>
-        <v/>
-      </c>
-      <c r="K29" s="100">
-        <f>J29+K28</f>
-        <v/>
-      </c>
-      <c r="L29" s="100">
-        <f>K29+L28</f>
-        <v/>
-      </c>
-      <c r="M29" s="100">
-        <f>L29+M28</f>
-        <v/>
-      </c>
-      <c r="N29" s="100">
-        <f>M29+N28</f>
-        <v/>
-      </c>
-      <c r="O29" s="100">
-        <f>N29+O28</f>
-        <v/>
-      </c>
-      <c r="P29" s="100">
-        <f>O29+P28</f>
-        <v/>
-      </c>
-      <c r="Q29" s="100">
-        <f>P29+Q28</f>
-        <v/>
-      </c>
-      <c r="R29" s="100">
-        <f>Q29+R28</f>
-        <v/>
-      </c>
-      <c r="S29" s="100">
-        <f>R29+S28</f>
-        <v/>
-      </c>
-      <c r="T29" s="100">
-        <f>S29+T28</f>
-        <v/>
-      </c>
-      <c r="U29" s="100">
-        <f>T29+U28</f>
-        <v/>
-      </c>
-      <c r="V29" s="100">
-        <f>U29+V28</f>
-        <v/>
-      </c>
-      <c r="W29" s="100">
-        <f>V29+W28</f>
-        <v/>
-      </c>
-      <c r="X29" s="100">
-        <f>W29+X28</f>
-        <v/>
-      </c>
-      <c r="Y29" s="100">
-        <f>X29+Y28</f>
-        <v/>
-      </c>
-      <c r="Z29" s="100">
-        <f>Y29+Z28</f>
-        <v/>
-      </c>
-      <c r="AA29" s="100">
-        <f>Z29+AA28</f>
-        <v/>
-      </c>
-      <c r="AB29" s="100">
-        <f>AA29+AB28</f>
-        <v/>
-      </c>
-      <c r="AC29" s="100">
-        <f>AB29+AC28</f>
-        <v/>
-      </c>
-      <c r="AD29" s="100">
-        <f>AC29+AD28</f>
-        <v/>
-      </c>
-      <c r="AE29" s="100">
-        <f>AD29+AE28</f>
-        <v/>
-      </c>
-      <c r="AF29" s="100">
-        <f>AE29+AF28</f>
-        <v/>
-      </c>
-      <c r="AG29" s="100">
-        <f>AF29+AG28</f>
-        <v/>
-      </c>
-      <c r="AH29" s="100">
-        <f>AG29+AH28</f>
-        <v/>
-      </c>
-      <c r="AI29" s="100">
-        <f>AH29+AI28</f>
-        <v/>
-      </c>
-      <c r="AJ29" s="100">
-        <f>AI29+AJ28</f>
-        <v/>
-      </c>
-      <c r="AK29" s="100">
-        <f>AJ29+AK28</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="96" t="n"/>
-      <c r="B30" s="91" t="n"/>
-      <c r="C30" s="91" t="n"/>
-      <c r="D30" s="91" t="n"/>
-      <c r="E30" s="91" t="n"/>
-      <c r="F30" s="91" t="n"/>
-      <c r="G30" s="91" t="n"/>
-      <c r="H30" s="91" t="n"/>
-      <c r="I30" s="91" t="n"/>
-      <c r="J30" s="91" t="n"/>
-      <c r="K30" s="91" t="n"/>
-      <c r="L30" s="91" t="n"/>
-      <c r="M30" s="91" t="n"/>
-      <c r="N30" s="91" t="n"/>
-      <c r="O30" s="91" t="n"/>
-      <c r="P30" s="91" t="n"/>
-      <c r="Q30" s="91" t="n"/>
-      <c r="R30" s="91" t="n"/>
-      <c r="S30" s="91" t="n"/>
-      <c r="T30" s="91" t="n"/>
-      <c r="U30" s="91" t="n"/>
-      <c r="V30" s="91" t="n"/>
-      <c r="W30" s="91" t="n"/>
-      <c r="X30" s="91" t="n"/>
-      <c r="Y30" s="91" t="n"/>
-      <c r="Z30" s="91" t="n"/>
-      <c r="AA30" s="91" t="n"/>
-      <c r="AB30" s="91" t="n"/>
-      <c r="AC30" s="91" t="n"/>
-      <c r="AD30" s="91" t="n"/>
-      <c r="AE30" s="91" t="n"/>
-      <c r="AF30" s="91" t="n"/>
-      <c r="AG30" s="91" t="n"/>
-      <c r="AH30" s="91" t="n"/>
-      <c r="AI30" s="91" t="n"/>
-      <c r="AJ30" s="91" t="n"/>
-      <c r="AK30" s="91" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="96" t="inlineStr">
-        <is>
-          <t>Yellow = inputs (edit). Green = formulas (don't overwrite).</t>
-        </is>
-      </c>
-      <c r="B31" s="91" t="n"/>
-      <c r="C31" s="91" t="n"/>
-      <c r="D31" s="91" t="n"/>
-      <c r="E31" s="91" t="n"/>
-      <c r="F31" s="91" t="n"/>
-      <c r="G31" s="91" t="n"/>
-      <c r="H31" s="91" t="n"/>
-      <c r="I31" s="91" t="n"/>
-      <c r="J31" s="91" t="n"/>
-      <c r="K31" s="91" t="n"/>
-      <c r="L31" s="91" t="n"/>
-      <c r="M31" s="91" t="n"/>
-      <c r="N31" s="91" t="n"/>
-      <c r="O31" s="91" t="n"/>
-      <c r="P31" s="91" t="n"/>
-      <c r="Q31" s="91" t="n"/>
-      <c r="R31" s="91" t="n"/>
-      <c r="S31" s="91" t="n"/>
-      <c r="T31" s="91" t="n"/>
-      <c r="U31" s="91" t="n"/>
-      <c r="V31" s="91" t="n"/>
-      <c r="W31" s="91" t="n"/>
-      <c r="X31" s="91" t="n"/>
-      <c r="Y31" s="91" t="n"/>
-      <c r="Z31" s="91" t="n"/>
-      <c r="AA31" s="91" t="n"/>
-      <c r="AB31" s="91" t="n"/>
-      <c r="AC31" s="91" t="n"/>
-      <c r="AD31" s="91" t="n"/>
-      <c r="AE31" s="91" t="n"/>
-      <c r="AF31" s="91" t="n"/>
-      <c r="AG31" s="91" t="n"/>
-      <c r="AH31" s="91" t="n"/>
-      <c r="AI31" s="91" t="n"/>
-      <c r="AJ31" s="91" t="n"/>
-      <c r="AK31" s="91" t="n"/>
+      <c r="B37" s="103">
+        <f>$B$9+B36+B34</f>
+        <v/>
+      </c>
+      <c r="C37" s="103">
+        <f>$B$9+C36+C34</f>
+        <v/>
+      </c>
+      <c r="D37" s="103">
+        <f>$B$9+D36+D34</f>
+        <v/>
+      </c>
+      <c r="E37" s="103">
+        <f>$B$9+E36+E34</f>
+        <v/>
+      </c>
+      <c r="F37" s="103">
+        <f>$B$9+F36+F34</f>
+        <v/>
+      </c>
+      <c r="G37" s="103">
+        <f>$B$9+G36+G34</f>
+        <v/>
+      </c>
+      <c r="H37" s="103">
+        <f>$B$9+H36+H34</f>
+        <v/>
+      </c>
+      <c r="I37" s="103">
+        <f>$B$9+I36+I34</f>
+        <v/>
+      </c>
+      <c r="J37" s="103">
+        <f>$B$9+J36+J34</f>
+        <v/>
+      </c>
+      <c r="K37" s="103">
+        <f>$B$9+K36+K34</f>
+        <v/>
+      </c>
+      <c r="L37" s="103">
+        <f>$B$9+L36+L34</f>
+        <v/>
+      </c>
+      <c r="M37" s="103">
+        <f>$B$9+M36+M34</f>
+        <v/>
+      </c>
+      <c r="N37" s="103">
+        <f>$B$9+N36+N34</f>
+        <v/>
+      </c>
+      <c r="O37" s="103">
+        <f>$B$9+O36+O34</f>
+        <v/>
+      </c>
+      <c r="P37" s="103">
+        <f>$B$9+P36+P34</f>
+        <v/>
+      </c>
+      <c r="Q37" s="103">
+        <f>$B$9+Q36+Q34</f>
+        <v/>
+      </c>
+      <c r="R37" s="103">
+        <f>$B$9+R36+R34</f>
+        <v/>
+      </c>
+      <c r="S37" s="103">
+        <f>$B$9+S36+S34</f>
+        <v/>
+      </c>
+      <c r="T37" s="103">
+        <f>$B$9+T36+T34</f>
+        <v/>
+      </c>
+      <c r="U37" s="103">
+        <f>$B$9+U36+U34</f>
+        <v/>
+      </c>
+      <c r="V37" s="103">
+        <f>$B$9+V36+V34</f>
+        <v/>
+      </c>
+      <c r="W37" s="103">
+        <f>$B$9+W36+W34</f>
+        <v/>
+      </c>
+      <c r="X37" s="103">
+        <f>$B$9+X36+X34</f>
+        <v/>
+      </c>
+      <c r="Y37" s="103">
+        <f>$B$9+Y36+Y34</f>
+        <v/>
+      </c>
+      <c r="Z37" s="103">
+        <f>$B$9+Z36+Z34</f>
+        <v/>
+      </c>
+      <c r="AA37" s="103">
+        <f>$B$9+AA36+AA34</f>
+        <v/>
+      </c>
+      <c r="AB37" s="103">
+        <f>$B$9+AB36+AB34</f>
+        <v/>
+      </c>
+      <c r="AC37" s="103">
+        <f>$B$9+AC36+AC34</f>
+        <v/>
+      </c>
+      <c r="AD37" s="103">
+        <f>$B$9+AD36+AD34</f>
+        <v/>
+      </c>
+      <c r="AE37" s="103">
+        <f>$B$9+AE36+AE34</f>
+        <v/>
+      </c>
+      <c r="AF37" s="103">
+        <f>$B$9+AF36+AF34</f>
+        <v/>
+      </c>
+      <c r="AG37" s="103">
+        <f>$B$9+AG36+AG34</f>
+        <v/>
+      </c>
+      <c r="AH37" s="103">
+        <f>$B$9+AH36+AH34</f>
+        <v/>
+      </c>
+      <c r="AI37" s="103">
+        <f>$B$9+AI36+AI34</f>
+        <v/>
+      </c>
+      <c r="AJ37" s="103">
+        <f>$B$9+AJ36+AJ34</f>
+        <v/>
+      </c>
+      <c r="AK37" s="103">
+        <f>$B$9+AK36+AK34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="102" t="inlineStr">
+        <is>
+          <t>Profit / (Loss)</t>
+        </is>
+      </c>
+      <c r="B38" s="103">
+        <f>B33-B37</f>
+        <v/>
+      </c>
+      <c r="C38" s="103">
+        <f>C33-C37</f>
+        <v/>
+      </c>
+      <c r="D38" s="103">
+        <f>D33-D37</f>
+        <v/>
+      </c>
+      <c r="E38" s="103">
+        <f>E33-E37</f>
+        <v/>
+      </c>
+      <c r="F38" s="103">
+        <f>F33-F37</f>
+        <v/>
+      </c>
+      <c r="G38" s="103">
+        <f>G33-G37</f>
+        <v/>
+      </c>
+      <c r="H38" s="103">
+        <f>H33-H37</f>
+        <v/>
+      </c>
+      <c r="I38" s="103">
+        <f>I33-I37</f>
+        <v/>
+      </c>
+      <c r="J38" s="103">
+        <f>J33-J37</f>
+        <v/>
+      </c>
+      <c r="K38" s="103">
+        <f>K33-K37</f>
+        <v/>
+      </c>
+      <c r="L38" s="103">
+        <f>L33-L37</f>
+        <v/>
+      </c>
+      <c r="M38" s="103">
+        <f>M33-M37</f>
+        <v/>
+      </c>
+      <c r="N38" s="103">
+        <f>N33-N37</f>
+        <v/>
+      </c>
+      <c r="O38" s="103">
+        <f>O33-O37</f>
+        <v/>
+      </c>
+      <c r="P38" s="103">
+        <f>P33-P37</f>
+        <v/>
+      </c>
+      <c r="Q38" s="103">
+        <f>Q33-Q37</f>
+        <v/>
+      </c>
+      <c r="R38" s="103">
+        <f>R33-R37</f>
+        <v/>
+      </c>
+      <c r="S38" s="103">
+        <f>S33-S37</f>
+        <v/>
+      </c>
+      <c r="T38" s="103">
+        <f>T33-T37</f>
+        <v/>
+      </c>
+      <c r="U38" s="103">
+        <f>U33-U37</f>
+        <v/>
+      </c>
+      <c r="V38" s="103">
+        <f>V33-V37</f>
+        <v/>
+      </c>
+      <c r="W38" s="103">
+        <f>W33-W37</f>
+        <v/>
+      </c>
+      <c r="X38" s="103">
+        <f>X33-X37</f>
+        <v/>
+      </c>
+      <c r="Y38" s="103">
+        <f>Y33-Y37</f>
+        <v/>
+      </c>
+      <c r="Z38" s="103">
+        <f>Z33-Z37</f>
+        <v/>
+      </c>
+      <c r="AA38" s="103">
+        <f>AA33-AA37</f>
+        <v/>
+      </c>
+      <c r="AB38" s="103">
+        <f>AB33-AB37</f>
+        <v/>
+      </c>
+      <c r="AC38" s="103">
+        <f>AC33-AC37</f>
+        <v/>
+      </c>
+      <c r="AD38" s="103">
+        <f>AD33-AD37</f>
+        <v/>
+      </c>
+      <c r="AE38" s="103">
+        <f>AE33-AE37</f>
+        <v/>
+      </c>
+      <c r="AF38" s="103">
+        <f>AF33-AF37</f>
+        <v/>
+      </c>
+      <c r="AG38" s="103">
+        <f>AG33-AG37</f>
+        <v/>
+      </c>
+      <c r="AH38" s="103">
+        <f>AH33-AH37</f>
+        <v/>
+      </c>
+      <c r="AI38" s="103">
+        <f>AI33-AI37</f>
+        <v/>
+      </c>
+      <c r="AJ38" s="103">
+        <f>AJ33-AJ37</f>
+        <v/>
+      </c>
+      <c r="AK38" s="103">
+        <f>AK33-AK37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="102" t="inlineStr">
+        <is>
+          <t>Cumulative Profit / (Loss)</t>
+        </is>
+      </c>
+      <c r="B39" s="103">
+        <f>B38</f>
+        <v/>
+      </c>
+      <c r="C39" s="103">
+        <f>B39+C38</f>
+        <v/>
+      </c>
+      <c r="D39" s="103">
+        <f>C39+D38</f>
+        <v/>
+      </c>
+      <c r="E39" s="103">
+        <f>D39+E38</f>
+        <v/>
+      </c>
+      <c r="F39" s="103">
+        <f>E39+F38</f>
+        <v/>
+      </c>
+      <c r="G39" s="103">
+        <f>F39+G38</f>
+        <v/>
+      </c>
+      <c r="H39" s="103">
+        <f>G39+H38</f>
+        <v/>
+      </c>
+      <c r="I39" s="103">
+        <f>H39+I38</f>
+        <v/>
+      </c>
+      <c r="J39" s="103">
+        <f>I39+J38</f>
+        <v/>
+      </c>
+      <c r="K39" s="103">
+        <f>J39+K38</f>
+        <v/>
+      </c>
+      <c r="L39" s="103">
+        <f>K39+L38</f>
+        <v/>
+      </c>
+      <c r="M39" s="103">
+        <f>L39+M38</f>
+        <v/>
+      </c>
+      <c r="N39" s="103">
+        <f>M39+N38</f>
+        <v/>
+      </c>
+      <c r="O39" s="103">
+        <f>N39+O38</f>
+        <v/>
+      </c>
+      <c r="P39" s="103">
+        <f>O39+P38</f>
+        <v/>
+      </c>
+      <c r="Q39" s="103">
+        <f>P39+Q38</f>
+        <v/>
+      </c>
+      <c r="R39" s="103">
+        <f>Q39+R38</f>
+        <v/>
+      </c>
+      <c r="S39" s="103">
+        <f>R39+S38</f>
+        <v/>
+      </c>
+      <c r="T39" s="103">
+        <f>S39+T38</f>
+        <v/>
+      </c>
+      <c r="U39" s="103">
+        <f>T39+U38</f>
+        <v/>
+      </c>
+      <c r="V39" s="103">
+        <f>U39+V38</f>
+        <v/>
+      </c>
+      <c r="W39" s="103">
+        <f>V39+W38</f>
+        <v/>
+      </c>
+      <c r="X39" s="103">
+        <f>W39+X38</f>
+        <v/>
+      </c>
+      <c r="Y39" s="103">
+        <f>X39+Y38</f>
+        <v/>
+      </c>
+      <c r="Z39" s="103">
+        <f>Y39+Z38</f>
+        <v/>
+      </c>
+      <c r="AA39" s="103">
+        <f>Z39+AA38</f>
+        <v/>
+      </c>
+      <c r="AB39" s="103">
+        <f>AA39+AB38</f>
+        <v/>
+      </c>
+      <c r="AC39" s="103">
+        <f>AB39+AC38</f>
+        <v/>
+      </c>
+      <c r="AD39" s="103">
+        <f>AC39+AD38</f>
+        <v/>
+      </c>
+      <c r="AE39" s="103">
+        <f>AD39+AE38</f>
+        <v/>
+      </c>
+      <c r="AF39" s="103">
+        <f>AE39+AF38</f>
+        <v/>
+      </c>
+      <c r="AG39" s="103">
+        <f>AF39+AG38</f>
+        <v/>
+      </c>
+      <c r="AH39" s="103">
+        <f>AG39+AH38</f>
+        <v/>
+      </c>
+      <c r="AI39" s="103">
+        <f>AH39+AI38</f>
+        <v/>
+      </c>
+      <c r="AJ39" s="103">
+        <f>AI39+AJ38</f>
+        <v/>
+      </c>
+      <c r="AK39" s="103">
+        <f>AJ39+AK38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="106" t="inlineStr">
+        <is>
+          <t>Yellow = inputs (edit). Green = formulas (do not overwrite).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="106" t="inlineStr">
+        <is>
+          <t>Cohort revenue is now driven by "Cohort seats sold this month". Default ramp: Cohort #1 (Jul 2026) = 3 seats target, ramping to 8 by Apr 2027. Edit yellow seat cells to test scenarios (Bull: 5/8/10/12; Bear: 1/2/3/5).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="106" t="inlineStr">
+        <is>
+          <t>Plan-installment revenue spreads N-pay sales over the next N months (N = "Payment plan months"). Lump-sum sales hit revenue in the cohort month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="106" t="inlineStr">
+        <is>
+          <t>See "Funnel" sheet for top-of-funnel math (views → email → challenge → cohort).</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="Z12:AK12"/>
-    <mergeCell ref="B12:M12"/>
-    <mergeCell ref="N12:Y12"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="62" customWidth="1" style="46" min="1" max="1"/>
+    <col width="16" customWidth="1" style="46" min="2" max="2"/>
+    <col width="45" customWidth="1" style="46" min="3" max="3"/>
+    <col width="16" customWidth="1" style="46" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="105" t="inlineStr">
+        <is>
+          <t>YouTube → Email → Challenge → Cohort funnel (planning sheet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="102" t="inlineStr">
+        <is>
+          <t>ASSUMPTIONS (edit yellow)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="45" t="inlineStr">
+        <is>
+          <t>Avg views / long-form video</t>
+        </is>
+      </c>
+      <c r="B4" s="101" t="n">
+        <v>800</v>
+      </c>
+      <c r="C4" s="45" t="inlineStr">
+        <is>
+          <t>first-90-day avg for new niche tech channel</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="45" t="inlineStr">
+        <is>
+          <t>Long-form videos / quarter</t>
+        </is>
+      </c>
+      <c r="B5" s="101" t="n">
+        <v>12</v>
+      </c>
+      <c r="C5" s="45" t="inlineStr">
+        <is>
+          <t>~1/wk</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="45" t="inlineStr">
+        <is>
+          <t>View → email subscriber %</t>
+        </is>
+      </c>
+      <c r="B6" s="101" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C6" s="45" t="inlineStr">
+        <is>
+          <t>0.3-1% realistic; 0.5% mid</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="45" t="inlineStr">
+        <is>
+          <t>Email subscriber → challenge ticket %</t>
+        </is>
+      </c>
+      <c r="B7" s="101" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C7" s="45" t="inlineStr">
+        <is>
+          <t>1-3% on a launch; 2% mid</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="45" t="inlineStr">
+        <is>
+          <t>Challenge ticket → cohort sale %</t>
+        </is>
+      </c>
+      <c r="B8" s="101" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C8" s="45" t="inlineStr">
+        <is>
+          <t>10-20% on a paid challenge; 12% mid</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="45" t="inlineStr">
+        <is>
+          <t>Cohort price ($)</t>
+        </is>
+      </c>
+      <c r="B9" s="101" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C9" s="45" t="inlineStr">
+        <is>
+          <t>flagship</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="45" t="inlineStr">
+        <is>
+          <t>Challenge ticket avg price ($)</t>
+        </is>
+      </c>
+      <c r="B10" s="101" t="n">
+        <v>130</v>
+      </c>
+      <c r="C10" s="45" t="inlineStr">
+        <is>
+          <t>blended GA $97 / VIP $297</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="102" t="inlineStr">
+        <is>
+          <t>SCENARIOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="45" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B13" s="45" t="inlineStr">
+        <is>
+          <t>Bear (0.5×)</t>
+        </is>
+      </c>
+      <c r="C13" s="45" t="inlineStr">
+        <is>
+          <t>Base (1×)</t>
+        </is>
+      </c>
+      <c r="D13" s="45" t="inlineStr">
+        <is>
+          <t>Bull (2×)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="45" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C14" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="45" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="45" t="inlineStr">
+        <is>
+          <t>Total views (per quarter)</t>
+        </is>
+      </c>
+      <c r="B15" s="103">
+        <f>$B$4*$B$5*B14</f>
+        <v/>
+      </c>
+      <c r="C15" s="103">
+        <f>$B$4*$B$5*C14</f>
+        <v/>
+      </c>
+      <c r="D15" s="103">
+        <f>$B$4*$B$5*D14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="45" t="inlineStr">
+        <is>
+          <t>Email signups (per quarter)</t>
+        </is>
+      </c>
+      <c r="B16" s="103">
+        <f>B15*$B$6</f>
+        <v/>
+      </c>
+      <c r="C16" s="103">
+        <f>C15*$B$6</f>
+        <v/>
+      </c>
+      <c r="D16" s="103">
+        <f>D15*$B$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="45" t="inlineStr">
+        <is>
+          <t>Challenge tickets (per quarter)</t>
+        </is>
+      </c>
+      <c r="B17" s="103">
+        <f>B16*$B$7</f>
+        <v/>
+      </c>
+      <c r="C17" s="103">
+        <f>C16*$B$7</f>
+        <v/>
+      </c>
+      <c r="D17" s="103">
+        <f>D16*$B$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="45" t="inlineStr">
+        <is>
+          <t>Cohort sales (per quarter)</t>
+        </is>
+      </c>
+      <c r="B18" s="103">
+        <f>B17*$B$8</f>
+        <v/>
+      </c>
+      <c r="C18" s="103">
+        <f>C17*$B$8</f>
+        <v/>
+      </c>
+      <c r="D18" s="103">
+        <f>D17*$B$8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="45" t="inlineStr">
+        <is>
+          <t>Cohort revenue ($/quarter)</t>
+        </is>
+      </c>
+      <c r="B19" s="103">
+        <f>B18*$B$9</f>
+        <v/>
+      </c>
+      <c r="C19" s="103">
+        <f>C18*$B$9</f>
+        <v/>
+      </c>
+      <c r="D19" s="103">
+        <f>D18*$B$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="45" t="inlineStr">
+        <is>
+          <t>Challenge revenue ($/quarter)</t>
+        </is>
+      </c>
+      <c r="B20" s="103">
+        <f>B17*$B$10</f>
+        <v/>
+      </c>
+      <c r="C20" s="103">
+        <f>C17*$B$10</f>
+        <v/>
+      </c>
+      <c r="D20" s="103">
+        <f>D17*$B$10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="45" t="inlineStr">
+        <is>
+          <t>Total revenue ($/quarter)</t>
+        </is>
+      </c>
+      <c r="B21" s="103">
+        <f>B19+B20</f>
+        <v/>
+      </c>
+      <c r="C21" s="103">
+        <f>C19+C20</f>
+        <v/>
+      </c>
+      <c r="D21" s="103">
+        <f>D19+D20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="102" t="inlineStr">
+        <is>
+          <t>WARM-NETWORK SUPPLEMENT (real life &gt; pure funnel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Cohort sales from LinkedIn warm DMs / quarter</t>
+        </is>
+      </c>
+      <c r="B24" s="101" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Cohort sales from referrals / quarter</t>
+        </is>
+      </c>
+      <c r="B25" s="101" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Cohort sales from existing list (&gt;500 subs already) / quarter</t>
+        </is>
+      </c>
+      <c r="B26" s="101" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Total warm-supplement seats / quarter</t>
+        </is>
+      </c>
+      <c r="B27" s="103">
+        <f>B24+B25+B26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="102" t="inlineStr">
+        <is>
+          <t>COMBINED Base seats per quarter (funnel + warm)</t>
+        </is>
+      </c>
+      <c r="B28" s="103">
+        <f>C18+B27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>COMBINED Base revenue per quarter</t>
+        </is>
+      </c>
+      <c r="B29" s="103">
+        <f>B28*$B$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="102" t="inlineStr">
+        <is>
+          <t>Notes:</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="45" t="inlineStr">
+        <is>
+          <t>* Funnel rates assume cold-start niche tech channel without paid ads. Adjust upward if existing audience &gt;1k engaged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="45" t="inlineStr">
+        <is>
+          <t>* "Email signups → challenge tickets" rate (2%) assumes the launch is to a fresh / newly-warmed list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="45" t="inlineStr">
+        <is>
+          <t>* "Challenge → cohort" 12% mid is the magic step — paid attendees convert ~10x free email leads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="45" t="inlineStr">
+        <is>
+          <t>* This sheet does NOT model compounding list growth. For W12 Cohort #1 plan, see "Ami — Projection" seat ramp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="45" t="inlineStr">
+        <is>
+          <t>* Realistic Cohort #1 (W12) target: 3 seats. Stretch: 5. Hitting 8 implies Bull-scenario top-of-funnel from W01.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4631,7 +5304,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4958,7 +5631,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
